--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -9468,7 +9468,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Måns Svensson</t>
+          <t>Måns Svensson, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY280"/>
+  <dimension ref="A1:AZ280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90848741</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128378420</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106193697</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128378443</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94962619</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134379592</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1447,6 +1482,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95126286</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1552,6 +1592,11 @@
           <t>C250065 AVK krokom och sveg</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128669966</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1659,6 +1704,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89723802</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1765,6 +1815,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90840157</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1906,6 +1961,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134806682</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2007,6 +2067,11 @@
           <t>C250065 AVK krokom och sveg</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128669970</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2137,6 +2202,11 @@
           <t>Internationell Herptilinventering med Svensk bas</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7298429</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2242,6 +2312,11 @@
           <t>C250065 AVK krokom och sveg</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128669969</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2343,6 +2418,11 @@
           <t>C250065 AVK krokom och sveg</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128673533</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2444,6 +2524,11 @@
           <t>C250065 AVK krokom och sveg</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128673534</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2545,6 +2630,11 @@
           <t>C250065 AVK krokom och sveg</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128673535</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2644,6 +2734,11 @@
       <c r="AY19" t="inlineStr">
         <is>
           <t>C250065 AVK krokom och sveg</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128669968</t>
         </is>
       </c>
     </row>
@@ -2748,6 +2843,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126872169</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2863,6 +2963,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126872155</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2975,6 +3080,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128274669</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3086,6 +3196,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563568</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3197,6 +3312,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563566</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3309,6 +3429,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122410602</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3430,6 +3555,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134282166</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3546,6 +3676,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104563569</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3668,6 +3803,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124526058</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3790,6 +3930,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124526177</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3917,6 +4062,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14984283</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4039,6 +4189,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14984284</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4146,6 +4301,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2568591</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4256,6 +4416,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128323610</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4366,6 +4531,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128329439</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4476,6 +4646,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128329963</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4583,6 +4758,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2665815</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4689,6 +4869,11 @@
           <t>C250065 AVK krokom och sveg</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128673541</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4795,6 +4980,11 @@
           <t>C250065 AVK krokom och sveg</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128673542</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4901,6 +5091,11 @@
           <t>C250065 AVK krokom och sveg</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128673543</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5007,6 +5202,11 @@
           <t>C250065 AVK krokom och sveg</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128673544</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5113,6 +5313,11 @@
           <t>C250065 AVK krokom och sveg</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128673545</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5220,6 +5425,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5023401</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5330,6 +5540,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128325061</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5437,6 +5652,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134831860</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5558,6 +5778,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109853204</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5675,6 +5900,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6744635</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5785,6 +6015,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6745338</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5895,6 +6130,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6745339</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6005,6 +6245,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6745340</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6115,6 +6360,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6745341</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6214,6 +6464,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71291449</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6336,6 +6591,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123226905</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6455,6 +6715,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/168811</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6561,6 +6826,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109227056</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6658,6 +6928,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134265083</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6782,6 +7057,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/248085</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6909,6 +7189,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123229155</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7015,6 +7300,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109227032</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7125,6 +7415,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/807417</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7235,6 +7530,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/807418</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7345,6 +7645,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/807419</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7464,6 +7769,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1865885</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7576,6 +7886,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123225922</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7686,6 +8001,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1882838</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7796,6 +8116,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1882839</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7906,6 +8231,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1882840</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8023,6 +8353,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123228988</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8156,6 +8491,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78491869</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8263,6 +8603,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95805188</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8370,6 +8715,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95805189</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8477,6 +8827,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95805190</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8584,6 +8939,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95805225</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8691,6 +9051,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95830149</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8798,6 +9163,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95830164</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8905,6 +9275,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95830166</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9017,6 +9392,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123225778</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9129,6 +9509,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123226621</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9239,6 +9624,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6537691</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9351,6 +9741,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123228716</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9472,6 +9867,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134831065</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9579,6 +9979,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134832464</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9686,6 +10091,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2285351</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9803,6 +10213,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61589795</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9909,6 +10324,11 @@
           <t>Utter barmarksinventering RMÖ/GDP</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105967727</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10026,6 +10446,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134294831</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10143,6 +10568,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134294874</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10251,6 +10681,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86189468</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10367,6 +10802,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133677345</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10484,6 +10924,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61591009</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10588,6 +11033,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61589823</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10707,6 +11157,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134005207</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10819,6 +11274,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61589764</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10920,6 +11380,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71769314</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11031,6 +11496,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/231352</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11138,6 +11608,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/231363</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11252,6 +11727,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/231364</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11372,6 +11852,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/231365</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11478,6 +11963,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6744711</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11595,6 +12085,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6745058</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11692,6 +12187,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124867241</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11798,6 +12298,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62055219</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11895,6 +12400,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124867263</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11992,6 +12502,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113012144</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12089,6 +12604,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124866986</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12186,6 +12706,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124866993</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12283,6 +12808,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124867151</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12380,6 +12910,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124867202</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12486,6 +13021,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2081430</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12592,6 +13132,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1857129</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12689,6 +13234,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113012091</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12786,6 +13336,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124866933</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12883,6 +13438,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124866939</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12980,6 +13540,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124867020</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13077,6 +13642,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124867041</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13174,6 +13744,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124867064</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13271,6 +13846,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124867204</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13368,6 +13948,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124867240</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13465,6 +14050,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124867270</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13562,6 +14152,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124867275</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13659,6 +14254,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124867379</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13756,6 +14356,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124867051</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13853,6 +14458,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124867193</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13950,6 +14560,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124867373</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14047,6 +14662,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124867203</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14164,6 +14784,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132654036</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14265,6 +14890,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113012135</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14362,6 +14992,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124867369</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14469,6 +15104,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86189694</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14576,6 +15216,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86189710</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14679,6 +15324,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86189726</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14782,6 +15432,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86189736</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14885,6 +15540,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86189762</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14988,6 +15648,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86321652</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15091,6 +15756,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86321919</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15194,6 +15864,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86322016</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15302,6 +15977,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86322037</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15405,6 +16085,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86322049</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15508,6 +16193,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86339644</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15611,6 +16301,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86339658</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15718,6 +16413,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86339688</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15821,6 +16521,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86339714</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15924,6 +16629,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86339731</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16027,6 +16737,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86339749</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16130,6 +16845,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86339787</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16233,6 +16953,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86339802</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16336,6 +17061,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86339810</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16439,6 +17169,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86339827</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16542,6 +17277,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86339840</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16645,6 +17385,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86339863</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16748,6 +17493,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86339890</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16851,6 +17601,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86339910</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16954,6 +17709,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86339918</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17061,6 +17821,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86339931</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17164,6 +17929,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86339949</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17267,6 +18037,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86339959</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17374,6 +18149,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86339969</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17481,6 +18261,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86339978</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17584,6 +18369,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86339986</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17691,6 +18481,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86340001</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17794,6 +18589,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86340011</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17897,6 +18697,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86340016</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18000,6 +18805,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86340037</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18103,6 +18913,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86340053</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18206,6 +19021,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86340090</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18313,6 +19133,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86340116</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18416,6 +19241,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86340155</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18519,6 +19349,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86340175</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18626,6 +19461,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86340186</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18733,6 +19573,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86340201</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18840,6 +19685,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86340208</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18943,6 +19793,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86340222</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19050,6 +19905,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86340296</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19153,6 +20013,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86354022</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -19256,6 +20121,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86354034</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -19359,6 +20229,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86354051</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19460,6 +20335,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113012108</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19579,6 +20459,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126054361</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19701,6 +20586,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60980662</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19803,6 +20693,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59820961</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19900,6 +20795,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104478322</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19997,6 +20897,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124867256</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -20114,6 +21019,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60980658</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -20231,6 +21141,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60980659</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -20348,6 +21263,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60980660</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -20465,6 +21385,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60980661</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -20577,6 +21502,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68435013</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20689,6 +21619,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68435014</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20801,6 +21736,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68435015</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -20913,6 +21853,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68435016</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -21025,6 +21970,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68435017</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -21137,6 +22087,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68435018</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -21249,6 +22204,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68435019</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -21365,6 +22325,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68435086</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -21481,6 +22446,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68435087</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -21598,6 +22568,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111775915</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -21715,6 +22690,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111776461</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -21812,6 +22792,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113012032</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -21909,6 +22894,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113012049</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -22006,6 +22996,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113012050</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -22108,6 +23103,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60215815</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -22205,6 +23205,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124867126</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -22302,6 +23307,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124867127</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -22423,6 +23433,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4540308</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -22525,6 +23540,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60065072</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -22627,6 +23647,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60065073</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -22729,6 +23754,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60065074</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -22850,6 +23880,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79447350</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -22961,6 +23996,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61231652</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -23063,6 +24103,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86321926</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -23165,6 +24210,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86354226</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -23262,6 +24312,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389463</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -23359,6 +24414,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389470</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -23456,6 +24516,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389493</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -23553,6 +24618,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305508</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -23650,6 +24720,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305099</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -23747,6 +24822,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305515</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -23844,6 +24924,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305516</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -23941,6 +25026,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305517</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -24038,6 +25128,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305518</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -24135,6 +25230,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389473</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -24232,6 +25332,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117831415</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -24332,6 +25437,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94446445</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -24433,6 +25543,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305839</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -24534,6 +25649,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305840</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -24635,6 +25755,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305841</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -24736,6 +25861,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305862</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -24837,6 +25967,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305863</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -24938,6 +26073,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305864</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -25044,6 +26184,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120306052</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -25150,6 +26295,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120306054</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -25251,6 +26401,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305975</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -25372,6 +26527,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4540065</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -25473,6 +26633,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305933</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -25574,6 +26739,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305934</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -25675,6 +26845,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305935</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -25776,6 +26951,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305936</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -25877,6 +27057,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305939</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -25978,6 +27163,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305941</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -26079,6 +27269,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305942</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -26180,6 +27375,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305943</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -26281,6 +27481,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305944</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -26382,6 +27587,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305945</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -26483,6 +27693,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305947</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -26584,6 +27799,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305948</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -26685,6 +27905,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305949</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -26786,6 +28011,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305950</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -26887,6 +28117,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305952</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -26988,6 +28223,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305953</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -27089,6 +28329,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305954</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -27190,6 +28435,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305955</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -27291,6 +28541,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305956</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -27392,6 +28647,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120306033</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -27489,6 +28749,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389502</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -27590,6 +28855,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
       </c>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111909859</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -27693,6 +28963,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94446308</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -27792,6 +29067,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94446527</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -27895,6 +29175,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86410369</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -27998,6 +29283,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86410388</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -28101,6 +29391,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86410413</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -28204,6 +29499,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86410432</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -28307,6 +29607,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86410459</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -28410,6 +29715,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86410475</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -28517,6 +29827,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86410497</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -28624,6 +29939,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86410510</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -28727,6 +30047,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86410524</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -28834,6 +30159,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86410541</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -28941,6 +30271,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86410556</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -29044,6 +30379,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86410573</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -29147,6 +30487,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86410592</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -29259,6 +30604,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121560121</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -29366,6 +30716,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119817264</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -29463,6 +30818,11 @@
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133884020</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -29565,6 +30925,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133884000</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -29680,6 +31045,11 @@
           <t>ÅGP-inventering björk och asp Norrland</t>
         </is>
       </c>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15772027</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -29800,6 +31170,11 @@
           <t>ÅGP-inventering björk och asp Norrland</t>
         </is>
       </c>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15772038</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -29915,6 +31290,11 @@
           <t>ÅGP-inventering björk och asp Norrland</t>
         </is>
       </c>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15771999</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -30035,6 +31415,11 @@
           <t>ÅGP-inventering björk och asp Norrland</t>
         </is>
       </c>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15772034</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -30150,6 +31535,11 @@
           <t>ÅGP-inventering björk och asp Norrland</t>
         </is>
       </c>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15771980</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -30265,6 +31655,11 @@
           <t>ÅGP-inventering björk och asp Norrland</t>
         </is>
       </c>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15772025</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -30385,8 +31780,294 @@
           <t>ÅGP-inventering björk och asp Norrland</t>
         </is>
       </c>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15772051</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -3440,7 +3440,7 @@
         <v>134282166</v>
       </c>
       <c r="B26" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>134294831</v>
       </c>
       <c r="B85" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         <v>134294874</v>
       </c>
       <c r="B86" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -1157,7 +1157,7 @@
         <v>135817118</v>
       </c>
       <c r="B6" t="n">
-        <v>106581</v>
+        <v>106583</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -1157,7 +1157,7 @@
         <v>135817118</v>
       </c>
       <c r="B6" t="n">
-        <v>106583</v>
+        <v>106603</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -1157,7 +1157,7 @@
         <v>135817118</v>
       </c>
       <c r="B6" t="n">
-        <v>106605</v>
+        <v>106606</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136150004</v>
       </c>
       <c r="B23" t="n">
-        <v>89431</v>
+        <v>89432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>136149902</v>
       </c>
       <c r="B24" t="n">
-        <v>92638</v>
+        <v>92639</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>136148101</v>
       </c>
       <c r="B27" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>136177837</v>
       </c>
       <c r="B206" t="n">
-        <v>106605</v>
+        <v>106606</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ287"/>
+  <dimension ref="A1:AZ288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1157,7 +1157,7 @@
         <v>135817118</v>
       </c>
       <c r="B6" t="n">
-        <v>106606</v>
+        <v>106607</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136150004</v>
       </c>
       <c r="B23" t="n">
-        <v>89432</v>
+        <v>89433</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>136149902</v>
       </c>
       <c r="B24" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>136148101</v>
       </c>
       <c r="B27" t="n">
-        <v>89296</v>
+        <v>89297</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>136148724</v>
       </c>
       <c r="B31" t="n">
-        <v>58086</v>
+        <v>58087</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -13117,62 +13117,51 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>136168429</v>
+        <v>136271230</v>
       </c>
       <c r="B109" t="n">
-        <v>79723</v>
+        <v>92067</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1816</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Luddig stiftdynlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Micarea hedlundii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Coppins</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>anamorf</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Bakut, Bakut, Jmt</t>
+          <t>Bakut, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>479847</v>
+        <v>479452</v>
       </c>
       <c r="R109" t="n">
-        <v>7019431</v>
+        <v>7019537</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13199,19 +13188,14 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>10:13</t>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13220,33 +13204,34 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Måns Svensson</t>
+          <t>Måns Svensson, Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136168429</t>
+          <t>https://artportalen.se/Sighting/136271230</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124866986</v>
+        <v>136168429</v>
       </c>
       <c r="B110" t="n">
-        <v>79327</v>
+        <v>79724</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13254,37 +13239,51 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>1816</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddig stiftdynlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Micarea hedlundii</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>Coppins</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>anamorf</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Bakut, Jmt</t>
+          <t>Bakut, Bakut, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>479503</v>
+        <v>479847</v>
       </c>
       <c r="R110" t="n">
-        <v>7019402</v>
+        <v>7019431</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13308,12 +13307,22 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13328,24 +13337,24 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>August Alvtegen Lundgren</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>August Alvtegen Lundgren</t>
+          <t>Alexander Hoffmann, Måns Svensson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124866986</t>
+          <t>https://artportalen.se/Sighting/136168429</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124866993</v>
+        <v>124866986</v>
       </c>
       <c r="B111" t="n">
         <v>79327</v>
@@ -13380,10 +13389,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>479981</v>
+        <v>479503</v>
       </c>
       <c r="R111" t="n">
-        <v>7019270</v>
+        <v>7019402</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13441,13 +13450,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124866993</t>
+          <t>https://artportalen.se/Sighting/124866986</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124867151</v>
+        <v>124866993</v>
       </c>
       <c r="B112" t="n">
         <v>79327</v>
@@ -13482,10 +13491,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>479805</v>
+        <v>479981</v>
       </c>
       <c r="R112" t="n">
-        <v>7019316</v>
+        <v>7019270</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13543,13 +13552,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124867151</t>
+          <t>https://artportalen.se/Sighting/124866993</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124867202</v>
+        <v>124867151</v>
       </c>
       <c r="B113" t="n">
         <v>79327</v>
@@ -13584,10 +13593,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>480021</v>
+        <v>479805</v>
       </c>
       <c r="R113" t="n">
-        <v>7019277</v>
+        <v>7019316</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13645,54 +13654,54 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124867202</t>
+          <t>https://artportalen.se/Sighting/124867151</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>2081430</v>
+        <v>124867202</v>
       </c>
       <c r="B114" t="n">
-        <v>80336</v>
+        <v>79327</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>(19E4h08), Jmt</t>
+          <t>Bakut, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>478495</v>
+        <v>480021</v>
       </c>
       <c r="R114" t="n">
-        <v>7019762</v>
+        <v>7019277</v>
       </c>
       <c r="S114" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13716,17 +13725,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>1993-10-28</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>1993-10-28</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>190447081 / LEP SATU / Enstaka-sparsam (1)  / ABR / OBJ.AREA:0,1 ha</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13741,53 +13745,49 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>August Alvtegen Lundgren</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Via Niklas Lönnell</t>
-        </is>
-      </c>
-      <c r="AY114" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens naturvärdesobjekt</t>
-        </is>
-      </c>
+          <t>August Alvtegen Lundgren</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2081430</t>
+          <t>https://artportalen.se/Sighting/124867202</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1857129</v>
+        <v>2081430</v>
       </c>
       <c r="B115" t="n">
-        <v>80432</v>
+        <v>80336</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13837,7 +13837,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>190447081 / LOB PULM / Tämligen allmän (2)  / ABR / OBJ.AREA:0,1 ha</t>
+          <t>190447081 / LEP SATU / Enstaka-sparsam (1)  / ABR / OBJ.AREA:0,1 ha</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13867,13 +13867,13 @@
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1857129</t>
+          <t>https://artportalen.se/Sighting/2081430</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>113012091</v>
+        <v>1857129</v>
       </c>
       <c r="B116" t="n">
         <v>80432</v>
@@ -13904,17 +13904,17 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Åsbacken, Jmt</t>
+          <t>(19E4h08), Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>479566</v>
+        <v>478495</v>
       </c>
       <c r="R116" t="n">
-        <v>7019381</v>
+        <v>7019762</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13938,12 +13938,17 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>1993-10-28</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>1993-10-28</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>190447081 / LOB PULM / Tämligen allmän (2)  / ABR / OBJ.AREA:0,1 ha</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13958,24 +13963,28 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr"/>
+          <t>Via Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113012091</t>
+          <t>https://artportalen.se/Sighting/1857129</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124866933</v>
+        <v>113012091</v>
       </c>
       <c r="B117" t="n">
         <v>80432</v>
@@ -14006,14 +14015,14 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Bakut, Jmt</t>
+          <t>Åsbacken, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>479592</v>
+        <v>479566</v>
       </c>
       <c r="R117" t="n">
-        <v>7019375</v>
+        <v>7019381</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14040,12 +14049,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14060,24 +14069,24 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>August Alvtegen Lundgren</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>August Alvtegen Lundgren</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124866933</t>
+          <t>https://artportalen.se/Sighting/113012091</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124866939</v>
+        <v>124866933</v>
       </c>
       <c r="B118" t="n">
         <v>80432</v>
@@ -14112,10 +14121,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>479608</v>
+        <v>479592</v>
       </c>
       <c r="R118" t="n">
-        <v>7019371</v>
+        <v>7019375</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14173,13 +14182,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124866939</t>
+          <t>https://artportalen.se/Sighting/124866933</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124867020</v>
+        <v>124866939</v>
       </c>
       <c r="B119" t="n">
         <v>80432</v>
@@ -14214,10 +14223,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>479988</v>
+        <v>479608</v>
       </c>
       <c r="R119" t="n">
-        <v>7019278</v>
+        <v>7019371</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14275,13 +14284,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124867020</t>
+          <t>https://artportalen.se/Sighting/124866939</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124867041</v>
+        <v>124867020</v>
       </c>
       <c r="B120" t="n">
         <v>80432</v>
@@ -14316,10 +14325,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>479932</v>
+        <v>479988</v>
       </c>
       <c r="R120" t="n">
-        <v>7019284</v>
+        <v>7019278</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14377,13 +14386,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124867041</t>
+          <t>https://artportalen.se/Sighting/124867020</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124867064</v>
+        <v>124867041</v>
       </c>
       <c r="B121" t="n">
         <v>80432</v>
@@ -14418,10 +14427,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>479903</v>
+        <v>479932</v>
       </c>
       <c r="R121" t="n">
-        <v>7019300</v>
+        <v>7019284</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14479,13 +14488,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124867064</t>
+          <t>https://artportalen.se/Sighting/124867041</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124867204</v>
+        <v>124867064</v>
       </c>
       <c r="B122" t="n">
         <v>80432</v>
@@ -14520,10 +14529,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>480018</v>
+        <v>479903</v>
       </c>
       <c r="R122" t="n">
-        <v>7019276</v>
+        <v>7019300</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14581,13 +14590,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124867204</t>
+          <t>https://artportalen.se/Sighting/124867064</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124867240</v>
+        <v>124867204</v>
       </c>
       <c r="B123" t="n">
         <v>80432</v>
@@ -14622,10 +14631,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>479713</v>
+        <v>480018</v>
       </c>
       <c r="R123" t="n">
-        <v>7019347</v>
+        <v>7019276</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14683,13 +14692,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124867240</t>
+          <t>https://artportalen.se/Sighting/124867204</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124867270</v>
+        <v>124867240</v>
       </c>
       <c r="B124" t="n">
         <v>80432</v>
@@ -14724,10 +14733,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>479715</v>
+        <v>479713</v>
       </c>
       <c r="R124" t="n">
-        <v>7019353</v>
+        <v>7019347</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14785,13 +14794,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124867270</t>
+          <t>https://artportalen.se/Sighting/124867240</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124867275</v>
+        <v>124867270</v>
       </c>
       <c r="B125" t="n">
         <v>80432</v>
@@ -14826,7 +14835,7 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>479719</v>
+        <v>479715</v>
       </c>
       <c r="R125" t="n">
         <v>7019353</v>
@@ -14887,13 +14896,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124867275</t>
+          <t>https://artportalen.se/Sighting/124867270</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>124867379</v>
+        <v>124867275</v>
       </c>
       <c r="B126" t="n">
         <v>80432</v>
@@ -14928,10 +14937,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>479876</v>
+        <v>479719</v>
       </c>
       <c r="R126" t="n">
-        <v>7019388</v>
+        <v>7019353</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14989,38 +14998,38 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124867379</t>
+          <t>https://artportalen.se/Sighting/124867275</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>124867051</v>
+        <v>124867379</v>
       </c>
       <c r="B127" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -15030,10 +15039,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>479988</v>
+        <v>479876</v>
       </c>
       <c r="R127" t="n">
-        <v>7019277</v>
+        <v>7019388</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15091,13 +15100,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124867051</t>
+          <t>https://artportalen.se/Sighting/124867379</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>124867193</v>
+        <v>124867051</v>
       </c>
       <c r="B128" t="n">
         <v>80461</v>
@@ -15132,10 +15141,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>479816</v>
+        <v>479988</v>
       </c>
       <c r="R128" t="n">
-        <v>7019313</v>
+        <v>7019277</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15193,13 +15202,13 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124867193</t>
+          <t>https://artportalen.se/Sighting/124867051</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>124867373</v>
+        <v>124867193</v>
       </c>
       <c r="B129" t="n">
         <v>80461</v>
@@ -15234,10 +15243,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>479879</v>
+        <v>479816</v>
       </c>
       <c r="R129" t="n">
-        <v>7019419</v>
+        <v>7019313</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15295,16 +15304,16 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124867373</t>
+          <t>https://artportalen.se/Sighting/124867193</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>124867203</v>
+        <v>124867373</v>
       </c>
       <c r="B130" t="n">
-        <v>57950</v>
+        <v>80461</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15312,21 +15321,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15336,10 +15345,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>480044</v>
+        <v>479879</v>
       </c>
       <c r="R130" t="n">
-        <v>7019257</v>
+        <v>7019419</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15397,33 +15406,33 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124867203</t>
+          <t>https://artportalen.se/Sighting/124867373</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>132654036</v>
+        <v>124867203</v>
       </c>
       <c r="B131" t="n">
-        <v>57975</v>
+        <v>57950</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -15432,24 +15441,19 @@
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>sågbäcken, Jmt</t>
+          <t>Bakut, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>479578</v>
+        <v>480044</v>
       </c>
       <c r="R131" t="n">
-        <v>7019493</v>
+        <v>7019257</v>
       </c>
       <c r="S131" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15473,27 +15477,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>11:41</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15508,69 +15497,70 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>August Alvtegen Lundgren</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>August Alvtegen Lundgren</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132654036</t>
+          <t>https://artportalen.se/Sighting/124867203</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>113012135</v>
+        <v>132654036</v>
       </c>
       <c r="B132" t="n">
-        <v>57141</v>
+        <v>57975</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Åsbacken, Jmt</t>
+          <t>sågbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>479856</v>
+        <v>479578</v>
       </c>
       <c r="R132" t="n">
-        <v>7019415</v>
+        <v>7019493</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15594,12 +15584,27 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15614,24 +15619,24 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113012135</t>
+          <t>https://artportalen.se/Sighting/132654036</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>124867369</v>
+        <v>113012135</v>
       </c>
       <c r="B133" t="n">
         <v>57141</v>
@@ -15659,17 +15664,21 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Bakut, Jmt</t>
+          <t>Åsbacken, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>479875</v>
+        <v>479856</v>
       </c>
       <c r="R133" t="n">
-        <v>7019399</v>
+        <v>7019415</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15696,12 +15705,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15716,74 +15725,65 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>August Alvtegen Lundgren</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>August Alvtegen Lundgren</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124867369</t>
+          <t>https://artportalen.se/Sighting/113012135</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>86189694</v>
+        <v>124867369</v>
       </c>
       <c r="B134" t="n">
-        <v>43249</v>
+        <v>57141</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>101248</v>
+        <v>100138</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Violett guldvinge</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lycaena helle</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Bakut, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>480017</v>
+        <v>479875</v>
       </c>
       <c r="R134" t="n">
-        <v>7019330</v>
+        <v>7019399</v>
       </c>
       <c r="S134" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15807,12 +15807,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2020-06-11</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2020-06-11</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15821,31 +15821,30 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Alvtegen Lundgren</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Alvtegen Lundgren</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86189694</t>
+          <t>https://artportalen.se/Sighting/124867369</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>86189710</v>
+        <v>86189694</v>
       </c>
       <c r="B135" t="n">
         <v>43249</v>
@@ -15875,7 +15874,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J135" t="inlineStr"/>
@@ -15889,10 +15888,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>479947</v>
+        <v>480017</v>
       </c>
       <c r="R135" t="n">
-        <v>7019354</v>
+        <v>7019330</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -15951,13 +15950,13 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86189710</t>
+          <t>https://artportalen.se/Sighting/86189694</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>86189726</v>
+        <v>86189710</v>
       </c>
       <c r="B136" t="n">
         <v>43249</v>
@@ -15985,7 +15984,11 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
@@ -15997,10 +16000,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>479891</v>
+        <v>479947</v>
       </c>
       <c r="R136" t="n">
-        <v>7019368</v>
+        <v>7019354</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -16059,13 +16062,13 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86189726</t>
+          <t>https://artportalen.se/Sighting/86189710</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>86189736</v>
+        <v>86189726</v>
       </c>
       <c r="B137" t="n">
         <v>43249</v>
@@ -16105,10 +16108,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>479783</v>
+        <v>479891</v>
       </c>
       <c r="R137" t="n">
-        <v>7019396</v>
+        <v>7019368</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -16167,13 +16170,13 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86189736</t>
+          <t>https://artportalen.se/Sighting/86189726</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>86189762</v>
+        <v>86189736</v>
       </c>
       <c r="B138" t="n">
         <v>43249</v>
@@ -16213,10 +16216,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>480825</v>
+        <v>479783</v>
       </c>
       <c r="R138" t="n">
-        <v>7019118</v>
+        <v>7019396</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -16275,13 +16278,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86189762</t>
+          <t>https://artportalen.se/Sighting/86189736</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>86321652</v>
+        <v>86189762</v>
       </c>
       <c r="B139" t="n">
         <v>43249</v>
@@ -16321,10 +16324,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>480322</v>
+        <v>480825</v>
       </c>
       <c r="R139" t="n">
-        <v>7019256</v>
+        <v>7019118</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -16351,12 +16354,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-06-11</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-06-11</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16383,13 +16386,13 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86321652</t>
+          <t>https://artportalen.se/Sighting/86189762</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>86321919</v>
+        <v>86321652</v>
       </c>
       <c r="B140" t="n">
         <v>43249</v>
@@ -16429,10 +16432,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>479974</v>
+        <v>480322</v>
       </c>
       <c r="R140" t="n">
-        <v>7019578</v>
+        <v>7019256</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -16491,13 +16494,13 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86321919</t>
+          <t>https://artportalen.se/Sighting/86321652</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>86322016</v>
+        <v>86321919</v>
       </c>
       <c r="B141" t="n">
         <v>43249</v>
@@ -16537,10 +16540,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>479983</v>
+        <v>479974</v>
       </c>
       <c r="R141" t="n">
-        <v>7019370</v>
+        <v>7019578</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -16599,13 +16602,13 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86322016</t>
+          <t>https://artportalen.se/Sighting/86321919</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>86322037</v>
+        <v>86322016</v>
       </c>
       <c r="B142" t="n">
         <v>43249</v>
@@ -16645,10 +16648,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>479342</v>
+        <v>479983</v>
       </c>
       <c r="R142" t="n">
-        <v>7019519</v>
+        <v>7019370</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -16683,11 +16686,6 @@
           <t>2020-06-17</t>
         </is>
       </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Rikligt med ormrot i ledningsgatan</t>
-        </is>
-      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -16712,13 +16710,13 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86322037</t>
+          <t>https://artportalen.se/Sighting/86322016</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>86322049</v>
+        <v>86322037</v>
       </c>
       <c r="B143" t="n">
         <v>43249</v>
@@ -16758,10 +16756,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>479018</v>
+        <v>479342</v>
       </c>
       <c r="R143" t="n">
-        <v>7019606</v>
+        <v>7019519</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -16796,6 +16794,11 @@
           <t>2020-06-17</t>
         </is>
       </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Rikligt med ormrot i ledningsgatan</t>
+        </is>
+      </c>
       <c r="AD143" t="b">
         <v>0</v>
       </c>
@@ -16820,13 +16823,13 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86322049</t>
+          <t>https://artportalen.se/Sighting/86322037</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>86339644</v>
+        <v>86322049</v>
       </c>
       <c r="B144" t="n">
         <v>43249</v>
@@ -16866,10 +16869,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>478626</v>
+        <v>479018</v>
       </c>
       <c r="R144" t="n">
-        <v>7019711</v>
+        <v>7019606</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -16896,12 +16899,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2020-06-18</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2020-06-18</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16928,13 +16931,13 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86339644</t>
+          <t>https://artportalen.se/Sighting/86322049</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>86339658</v>
+        <v>86339644</v>
       </c>
       <c r="B145" t="n">
         <v>43249</v>
@@ -16974,10 +16977,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>478551</v>
+        <v>478626</v>
       </c>
       <c r="R145" t="n">
-        <v>7019734</v>
+        <v>7019711</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -17036,13 +17039,13 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86339658</t>
+          <t>https://artportalen.se/Sighting/86339644</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>86339688</v>
+        <v>86339658</v>
       </c>
       <c r="B146" t="n">
         <v>43249</v>
@@ -17070,11 +17073,7 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
@@ -17086,10 +17085,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>478528</v>
+        <v>478551</v>
       </c>
       <c r="R146" t="n">
-        <v>7019744</v>
+        <v>7019734</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -17148,13 +17147,13 @@
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86339688</t>
+          <t>https://artportalen.se/Sighting/86339658</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>86339714</v>
+        <v>86339688</v>
       </c>
       <c r="B147" t="n">
         <v>43249</v>
@@ -17182,7 +17181,11 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
@@ -17194,10 +17197,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>478489</v>
+        <v>478528</v>
       </c>
       <c r="R147" t="n">
-        <v>7019749</v>
+        <v>7019744</v>
       </c>
       <c r="S147" t="n">
         <v>25</v>
@@ -17256,13 +17259,13 @@
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86339714</t>
+          <t>https://artportalen.se/Sighting/86339688</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>86339731</v>
+        <v>86339714</v>
       </c>
       <c r="B148" t="n">
         <v>43249</v>
@@ -17302,10 +17305,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>478417</v>
+        <v>478489</v>
       </c>
       <c r="R148" t="n">
-        <v>7019774</v>
+        <v>7019749</v>
       </c>
       <c r="S148" t="n">
         <v>25</v>
@@ -17364,13 +17367,13 @@
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86339731</t>
+          <t>https://artportalen.se/Sighting/86339714</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>86339749</v>
+        <v>86339731</v>
       </c>
       <c r="B149" t="n">
         <v>43249</v>
@@ -17410,10 +17413,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>478037</v>
+        <v>478417</v>
       </c>
       <c r="R149" t="n">
-        <v>7019873</v>
+        <v>7019774</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -17435,7 +17438,7 @@
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>Rödön</t>
+          <t>Ås</t>
         </is>
       </c>
       <c r="Y149" t="inlineStr">
@@ -17472,13 +17475,13 @@
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86339749</t>
+          <t>https://artportalen.se/Sighting/86339731</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>86339787</v>
+        <v>86339749</v>
       </c>
       <c r="B150" t="n">
         <v>43249</v>
@@ -17518,10 +17521,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>477774</v>
+        <v>478037</v>
       </c>
       <c r="R150" t="n">
-        <v>7019946</v>
+        <v>7019873</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -17580,13 +17583,13 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86339787</t>
+          <t>https://artportalen.se/Sighting/86339749</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>86339802</v>
+        <v>86339787</v>
       </c>
       <c r="B151" t="n">
         <v>43249</v>
@@ -17626,10 +17629,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>477363</v>
+        <v>477774</v>
       </c>
       <c r="R151" t="n">
-        <v>7020052</v>
+        <v>7019946</v>
       </c>
       <c r="S151" t="n">
         <v>25</v>
@@ -17688,13 +17691,13 @@
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86339802</t>
+          <t>https://artportalen.se/Sighting/86339787</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>86339810</v>
+        <v>86339802</v>
       </c>
       <c r="B152" t="n">
         <v>43249</v>
@@ -17734,10 +17737,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>477238</v>
+        <v>477363</v>
       </c>
       <c r="R152" t="n">
-        <v>7020089</v>
+        <v>7020052</v>
       </c>
       <c r="S152" t="n">
         <v>25</v>
@@ -17796,13 +17799,13 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86339810</t>
+          <t>https://artportalen.se/Sighting/86339802</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>86339827</v>
+        <v>86339810</v>
       </c>
       <c r="B153" t="n">
         <v>43249</v>
@@ -17842,10 +17845,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>476121</v>
+        <v>477238</v>
       </c>
       <c r="R153" t="n">
-        <v>7020399</v>
+        <v>7020089</v>
       </c>
       <c r="S153" t="n">
         <v>25</v>
@@ -17904,13 +17907,13 @@
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86339827</t>
+          <t>https://artportalen.se/Sighting/86339810</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>86339840</v>
+        <v>86339827</v>
       </c>
       <c r="B154" t="n">
         <v>43249</v>
@@ -17950,10 +17953,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>475930</v>
+        <v>476121</v>
       </c>
       <c r="R154" t="n">
-        <v>7020445</v>
+        <v>7020399</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -18012,13 +18015,13 @@
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86339840</t>
+          <t>https://artportalen.se/Sighting/86339827</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>86339863</v>
+        <v>86339840</v>
       </c>
       <c r="B155" t="n">
         <v>43249</v>
@@ -18058,10 +18061,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>475579</v>
+        <v>475930</v>
       </c>
       <c r="R155" t="n">
-        <v>7020541</v>
+        <v>7020445</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -18120,13 +18123,13 @@
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86339863</t>
+          <t>https://artportalen.se/Sighting/86339840</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>86339890</v>
+        <v>86339863</v>
       </c>
       <c r="B156" t="n">
         <v>43249</v>
@@ -18166,10 +18169,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>475156</v>
+        <v>475579</v>
       </c>
       <c r="R156" t="n">
-        <v>7020655</v>
+        <v>7020541</v>
       </c>
       <c r="S156" t="n">
         <v>25</v>
@@ -18228,13 +18231,13 @@
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86339890</t>
+          <t>https://artportalen.se/Sighting/86339863</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>86339910</v>
+        <v>86339890</v>
       </c>
       <c r="B157" t="n">
         <v>43249</v>
@@ -18274,10 +18277,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>475478</v>
+        <v>475156</v>
       </c>
       <c r="R157" t="n">
-        <v>7020563</v>
+        <v>7020655</v>
       </c>
       <c r="S157" t="n">
         <v>25</v>
@@ -18336,13 +18339,13 @@
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86339910</t>
+          <t>https://artportalen.se/Sighting/86339890</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>86339918</v>
+        <v>86339910</v>
       </c>
       <c r="B158" t="n">
         <v>43249</v>
@@ -18382,10 +18385,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>475548</v>
+        <v>475478</v>
       </c>
       <c r="R158" t="n">
-        <v>7020546</v>
+        <v>7020563</v>
       </c>
       <c r="S158" t="n">
         <v>25</v>
@@ -18444,13 +18447,13 @@
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86339918</t>
+          <t>https://artportalen.se/Sighting/86339910</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>86339931</v>
+        <v>86339918</v>
       </c>
       <c r="B159" t="n">
         <v>43249</v>
@@ -18478,11 +18481,7 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
@@ -18494,10 +18493,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>475580</v>
+        <v>475548</v>
       </c>
       <c r="R159" t="n">
-        <v>7020537</v>
+        <v>7020546</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -18556,13 +18555,13 @@
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86339931</t>
+          <t>https://artportalen.se/Sighting/86339918</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>86339949</v>
+        <v>86339931</v>
       </c>
       <c r="B160" t="n">
         <v>43249</v>
@@ -18590,7 +18589,11 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr"/>
@@ -18602,10 +18605,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>475863</v>
+        <v>475580</v>
       </c>
       <c r="R160" t="n">
-        <v>7020458</v>
+        <v>7020537</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -18664,13 +18667,13 @@
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86339949</t>
+          <t>https://artportalen.se/Sighting/86339931</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>86339959</v>
+        <v>86339949</v>
       </c>
       <c r="B161" t="n">
         <v>43249</v>
@@ -18710,10 +18713,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>476179</v>
+        <v>475863</v>
       </c>
       <c r="R161" t="n">
-        <v>7020377</v>
+        <v>7020458</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -18772,13 +18775,13 @@
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86339959</t>
+          <t>https://artportalen.se/Sighting/86339949</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>86339969</v>
+        <v>86339959</v>
       </c>
       <c r="B162" t="n">
         <v>43249</v>
@@ -18806,11 +18809,7 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
@@ -18822,10 +18821,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>477240</v>
+        <v>476179</v>
       </c>
       <c r="R162" t="n">
-        <v>7020088</v>
+        <v>7020377</v>
       </c>
       <c r="S162" t="n">
         <v>25</v>
@@ -18884,13 +18883,13 @@
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86339969</t>
+          <t>https://artportalen.se/Sighting/86339959</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>86339978</v>
+        <v>86339969</v>
       </c>
       <c r="B163" t="n">
         <v>43249</v>
@@ -18934,10 +18933,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>477267</v>
+        <v>477240</v>
       </c>
       <c r="R163" t="n">
-        <v>7020082</v>
+        <v>7020088</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -18996,13 +18995,13 @@
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86339978</t>
+          <t>https://artportalen.se/Sighting/86339969</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>86339986</v>
+        <v>86339978</v>
       </c>
       <c r="B164" t="n">
         <v>43249</v>
@@ -19030,7 +19029,11 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
@@ -19042,10 +19045,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>477313</v>
+        <v>477267</v>
       </c>
       <c r="R164" t="n">
-        <v>7020068</v>
+        <v>7020082</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -19104,13 +19107,13 @@
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86339986</t>
+          <t>https://artportalen.se/Sighting/86339978</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>86340001</v>
+        <v>86339986</v>
       </c>
       <c r="B165" t="n">
         <v>43249</v>
@@ -19138,11 +19141,7 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
@@ -19154,10 +19153,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>477449</v>
+        <v>477313</v>
       </c>
       <c r="R165" t="n">
-        <v>7020028</v>
+        <v>7020068</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -19216,13 +19215,13 @@
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86340001</t>
+          <t>https://artportalen.se/Sighting/86339986</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>86340011</v>
+        <v>86340001</v>
       </c>
       <c r="B166" t="n">
         <v>43249</v>
@@ -19250,7 +19249,11 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr"/>
@@ -19262,10 +19265,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>477934</v>
+        <v>477449</v>
       </c>
       <c r="R166" t="n">
-        <v>7019900</v>
+        <v>7020028</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -19324,13 +19327,13 @@
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86340011</t>
+          <t>https://artportalen.se/Sighting/86340001</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>86340016</v>
+        <v>86340011</v>
       </c>
       <c r="B167" t="n">
         <v>43249</v>
@@ -19370,10 +19373,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>478110</v>
+        <v>477934</v>
       </c>
       <c r="R167" t="n">
-        <v>7019849</v>
+        <v>7019900</v>
       </c>
       <c r="S167" t="n">
         <v>25</v>
@@ -19395,7 +19398,7 @@
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>Ås</t>
+          <t>Rödön</t>
         </is>
       </c>
       <c r="Y167" t="inlineStr">
@@ -19432,13 +19435,13 @@
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86340016</t>
+          <t>https://artportalen.se/Sighting/86340011</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>86340037</v>
+        <v>86340016</v>
       </c>
       <c r="B168" t="n">
         <v>43249</v>
@@ -19478,10 +19481,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>478227</v>
+        <v>478110</v>
       </c>
       <c r="R168" t="n">
-        <v>7019818</v>
+        <v>7019849</v>
       </c>
       <c r="S168" t="n">
         <v>25</v>
@@ -19540,13 +19543,13 @@
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86340037</t>
+          <t>https://artportalen.se/Sighting/86340016</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>86340053</v>
+        <v>86340037</v>
       </c>
       <c r="B169" t="n">
         <v>43249</v>
@@ -19586,10 +19589,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>478536</v>
+        <v>478227</v>
       </c>
       <c r="R169" t="n">
-        <v>7019734</v>
+        <v>7019818</v>
       </c>
       <c r="S169" t="n">
         <v>25</v>
@@ -19648,13 +19651,13 @@
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86340053</t>
+          <t>https://artportalen.se/Sighting/86340037</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>86340090</v>
+        <v>86340053</v>
       </c>
       <c r="B170" t="n">
         <v>43249</v>
@@ -19694,10 +19697,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>479034</v>
+        <v>478536</v>
       </c>
       <c r="R170" t="n">
-        <v>7019601</v>
+        <v>7019734</v>
       </c>
       <c r="S170" t="n">
         <v>25</v>
@@ -19756,13 +19759,13 @@
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86340090</t>
+          <t>https://artportalen.se/Sighting/86340053</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>86340116</v>
+        <v>86340090</v>
       </c>
       <c r="B171" t="n">
         <v>43249</v>
@@ -19790,11 +19793,7 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr"/>
@@ -19806,10 +19805,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>479040</v>
+        <v>479034</v>
       </c>
       <c r="R171" t="n">
-        <v>7019646</v>
+        <v>7019601</v>
       </c>
       <c r="S171" t="n">
         <v>25</v>
@@ -19868,13 +19867,13 @@
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86340116</t>
+          <t>https://artportalen.se/Sighting/86340090</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>86340155</v>
+        <v>86340116</v>
       </c>
       <c r="B172" t="n">
         <v>43249</v>
@@ -19902,7 +19901,11 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr"/>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr"/>
@@ -19914,10 +19917,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>479227</v>
+        <v>479040</v>
       </c>
       <c r="R172" t="n">
-        <v>7019549</v>
+        <v>7019646</v>
       </c>
       <c r="S172" t="n">
         <v>25</v>
@@ -19976,13 +19979,13 @@
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86340155</t>
+          <t>https://artportalen.se/Sighting/86340116</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>86340175</v>
+        <v>86340155</v>
       </c>
       <c r="B173" t="n">
         <v>43249</v>
@@ -20022,10 +20025,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>479243</v>
+        <v>479227</v>
       </c>
       <c r="R173" t="n">
-        <v>7019545</v>
+        <v>7019549</v>
       </c>
       <c r="S173" t="n">
         <v>25</v>
@@ -20084,13 +20087,13 @@
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86340175</t>
+          <t>https://artportalen.se/Sighting/86340155</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>86340186</v>
+        <v>86340175</v>
       </c>
       <c r="B174" t="n">
         <v>43249</v>
@@ -20118,11 +20121,7 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr"/>
@@ -20134,10 +20133,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>479305</v>
+        <v>479243</v>
       </c>
       <c r="R174" t="n">
-        <v>7019527</v>
+        <v>7019545</v>
       </c>
       <c r="S174" t="n">
         <v>25</v>
@@ -20196,13 +20195,13 @@
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86340186</t>
+          <t>https://artportalen.se/Sighting/86340175</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>86340201</v>
+        <v>86340186</v>
       </c>
       <c r="B175" t="n">
         <v>43249</v>
@@ -20232,7 +20231,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J175" t="inlineStr"/>
@@ -20246,10 +20245,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>479353</v>
+        <v>479305</v>
       </c>
       <c r="R175" t="n">
-        <v>7019514</v>
+        <v>7019527</v>
       </c>
       <c r="S175" t="n">
         <v>25</v>
@@ -20308,13 +20307,13 @@
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86340201</t>
+          <t>https://artportalen.se/Sighting/86340186</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>86340208</v>
+        <v>86340201</v>
       </c>
       <c r="B176" t="n">
         <v>43249</v>
@@ -20358,10 +20357,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>479482</v>
+        <v>479353</v>
       </c>
       <c r="R176" t="n">
-        <v>7019479</v>
+        <v>7019514</v>
       </c>
       <c r="S176" t="n">
         <v>25</v>
@@ -20420,13 +20419,13 @@
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86340208</t>
+          <t>https://artportalen.se/Sighting/86340201</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>86340222</v>
+        <v>86340208</v>
       </c>
       <c r="B177" t="n">
         <v>43249</v>
@@ -20454,7 +20453,11 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr"/>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
@@ -20466,10 +20469,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>479582</v>
+        <v>479482</v>
       </c>
       <c r="R177" t="n">
-        <v>7019455</v>
+        <v>7019479</v>
       </c>
       <c r="S177" t="n">
         <v>25</v>
@@ -20528,13 +20531,13 @@
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86340222</t>
+          <t>https://artportalen.se/Sighting/86340208</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>86340296</v>
+        <v>86340222</v>
       </c>
       <c r="B178" t="n">
         <v>43249</v>
@@ -20562,11 +20565,7 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr"/>
@@ -20578,10 +20577,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>479612</v>
+        <v>479582</v>
       </c>
       <c r="R178" t="n">
-        <v>7019444</v>
+        <v>7019455</v>
       </c>
       <c r="S178" t="n">
         <v>25</v>
@@ -20640,13 +20639,13 @@
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86340296</t>
+          <t>https://artportalen.se/Sighting/86340222</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>86354022</v>
+        <v>86340296</v>
       </c>
       <c r="B179" t="n">
         <v>43249</v>
@@ -20674,7 +20673,11 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr"/>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr"/>
@@ -20686,10 +20689,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>479431</v>
+        <v>479612</v>
       </c>
       <c r="R179" t="n">
-        <v>7020819</v>
+        <v>7019444</v>
       </c>
       <c r="S179" t="n">
         <v>25</v>
@@ -20716,12 +20719,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2020-06-19</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2020-06-19</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20748,13 +20751,13 @@
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86354022</t>
+          <t>https://artportalen.se/Sighting/86340296</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>86354034</v>
+        <v>86354022</v>
       </c>
       <c r="B180" t="n">
         <v>43249</v>
@@ -20794,10 +20797,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>479383</v>
+        <v>479431</v>
       </c>
       <c r="R180" t="n">
-        <v>7020864</v>
+        <v>7020819</v>
       </c>
       <c r="S180" t="n">
         <v>25</v>
@@ -20856,13 +20859,13 @@
       <c r="AY180" t="inlineStr"/>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86354034</t>
+          <t>https://artportalen.se/Sighting/86354022</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>86354051</v>
+        <v>86354034</v>
       </c>
       <c r="B181" t="n">
         <v>43249</v>
@@ -20902,10 +20905,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>479460</v>
+        <v>479383</v>
       </c>
       <c r="R181" t="n">
-        <v>7020720</v>
+        <v>7020864</v>
       </c>
       <c r="S181" t="n">
         <v>25</v>
@@ -20964,58 +20967,59 @@
       <c r="AY181" t="inlineStr"/>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86354051</t>
+          <t>https://artportalen.se/Sighting/86354034</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>113012108</v>
+        <v>86354051</v>
       </c>
       <c r="B182" t="n">
-        <v>57144</v>
+        <v>43249</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>102613</v>
+        <v>101248</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Violett guldvinge</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Lycaena helle</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Åsbacken, Jmt</t>
+          <t>Bakut, Jmt</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>479426</v>
+        <v>479460</v>
       </c>
       <c r="R182" t="n">
-        <v>7019491</v>
+        <v>7020720</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -21039,12 +21043,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2020-06-19</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2020-06-19</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21053,50 +21057,51 @@
       <c r="AE182" t="b">
         <v>0</v>
       </c>
+      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
       </c>
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113012108</t>
+          <t>https://artportalen.se/Sighting/86354051</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>126054361</v>
+        <v>113012108</v>
       </c>
       <c r="B183" t="n">
-        <v>58497</v>
+        <v>57144</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>102990</v>
+        <v>102613</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -21106,30 +21111,22 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N183" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Bodstaden, Jmt</t>
+          <t>Åsbacken, Jmt</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>480437</v>
+        <v>479426</v>
       </c>
       <c r="R183" t="n">
-        <v>7019188</v>
+        <v>7019491</v>
       </c>
       <c r="S183" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -21153,22 +21150,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="Z183" t="inlineStr">
-        <is>
-          <t>17:31</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AB183" t="inlineStr">
-        <is>
-          <t>17:31</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21183,27 +21170,27 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Niklas Holmström</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Niklas Holmström</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126054361</t>
+          <t>https://artportalen.se/Sighting/113012108</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>60980662</v>
+        <v>126054361</v>
       </c>
       <c r="B184" t="n">
-        <v>109815</v>
+        <v>58497</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21211,52 +21198,49 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>220204</v>
+        <v>102990</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Sakrisbodarna / 150 m S /, kraftledning, Jmt</t>
+          <t>Bodstaden, Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>478968</v>
+        <v>480437</v>
       </c>
       <c r="R184" t="n">
-        <v>7019621</v>
+        <v>7019188</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21280,17 +21264,22 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2016-08-13</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2016-08-13</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>23 ex i fröspridning/överblommade (2 fortfarande i blom) längs 14 m serviceväg i kraftledning. Torrare del nedskuren i kulle.</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21301,74 +21290,84 @@
       </c>
       <c r="AG184" t="b">
         <v>0</v>
-      </c>
-      <c r="AI184" t="inlineStr">
-        <is>
-          <t>kraftledningsgata</t>
-        </is>
       </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Niklas Holmström</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Niklas Holmström</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60980662</t>
+          <t>https://artportalen.se/Sighting/126054361</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>59820961</v>
+        <v>60980662</v>
       </c>
       <c r="B185" t="n">
-        <v>99118</v>
+        <v>109815</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>220787</v>
+        <v>220204</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Tängskogen, Sågbäcken, södra delen, ca 0 - 50 m söder om kraftledningen,, Jmt</t>
+          <t>Sakrisbodarna / 150 m S /, kraftledning, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>478496</v>
+        <v>478968</v>
       </c>
       <c r="R185" t="n">
-        <v>7019710</v>
+        <v>7019621</v>
       </c>
       <c r="S185" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21392,17 +21391,17 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2000-07-15</t>
+          <t>2016-08-13</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2000-07-15</t>
+          <t>2016-08-13</t>
         </is>
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, örtrik bäckdråg,</t>
+          <t>23 ex i fröspridning/överblommade (2 fortfarande i blom) längs 14 m serviceväg i kraftledning. Torrare del nedskuren i kulle.</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21413,28 +21412,33 @@
       </c>
       <c r="AG185" t="b">
         <v>0</v>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>kraftledningsgata</t>
+        </is>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Bengt Petterson</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/59820961</t>
+          <t>https://artportalen.se/Sighting/60980662</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>104478322</v>
+        <v>59820961</v>
       </c>
       <c r="B186" t="n">
         <v>99118</v>
@@ -21465,17 +21469,17 @@
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Patronbodarna, Jmt</t>
+          <t>Tängskogen, Sågbäcken, södra delen, ca 0 - 50 m söder om kraftledningen,, Jmt</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>478471</v>
+        <v>478496</v>
       </c>
       <c r="R186" t="n">
-        <v>7019680</v>
+        <v>7019710</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21499,12 +21503,17 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2022-11-04</t>
+          <t>2000-07-15</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2022-11-04</t>
+          <t>2000-07-15</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, örtrik bäckdråg,</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21519,24 +21528,24 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Benny Öwre, Johan Råghall, Kristofer Holmsten</t>
+          <t>Bengt Petterson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104478322</t>
+          <t>https://artportalen.se/Sighting/59820961</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>124867256</v>
+        <v>104478322</v>
       </c>
       <c r="B187" t="n">
         <v>99118</v>
@@ -21567,14 +21576,14 @@
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Bakut, Jmt</t>
+          <t>Patronbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>479634</v>
+        <v>478471</v>
       </c>
       <c r="R187" t="n">
-        <v>7019379</v>
+        <v>7019680</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21601,12 +21610,12 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21621,27 +21630,27 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>August Alvtegen Lundgren</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>August Alvtegen Lundgren</t>
+          <t>Benny Öwre, Johan Råghall, Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124867256</t>
+          <t>https://artportalen.se/Sighting/104478322</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>60980658</v>
+        <v>124867256</v>
       </c>
       <c r="B188" t="n">
-        <v>106414</v>
+        <v>99118</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21649,44 +21658,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>221447</v>
+        <v>220787</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Ås Backen 11:1, kraftledning 680 m V om väg 745, Jmt</t>
+          <t>Bakut, Jmt</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>479743</v>
+        <v>479634</v>
       </c>
       <c r="R188" t="n">
-        <v>7019415</v>
+        <v>7019379</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21713,17 +21712,12 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2016-08-13</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2016-08-13</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>1 ex i blom. Blå. På serviceväg i kraftledningsgata. Torrare del nedskuren i kulle. Servicearbete pågår, vägen allt mer sönderkörd. Gentianan mitt mellan krafiga hjulspår.</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21734,33 +21728,28 @@
       </c>
       <c r="AG188" t="b">
         <v>0</v>
-      </c>
-      <c r="AI188" t="inlineStr">
-        <is>
-          <t>kraftledningsgata</t>
-        </is>
       </c>
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>August Alvtegen Lundgren</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>August Alvtegen Lundgren</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60980658</t>
+          <t>https://artportalen.se/Sighting/124867256</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>60980659</v>
+        <v>60980658</v>
       </c>
       <c r="B189" t="n">
         <v>106414</v>
@@ -21786,7 +21775,7 @@
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -21801,17 +21790,17 @@
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Ås Backen 11:1, kraftledning 700 m V om väg 745, Jmt</t>
+          <t>Ås Backen 11:1, kraftledning 680 m V om väg 745, Jmt</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>479702</v>
+        <v>479743</v>
       </c>
       <c r="R189" t="n">
-        <v>7019422</v>
+        <v>7019415</v>
       </c>
       <c r="S189" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -21845,7 +21834,7 @@
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>64 ex i blom spridda längs 36 m serviceväg i kraftledning. Blå blommor. Torrare del nedskuren i kulle. Servicearbete pågår, men ännu har man inte nått denna del av vägen.</t>
+          <t>1 ex i blom. Blå. På serviceväg i kraftledningsgata. Torrare del nedskuren i kulle. Servicearbete pågår, vägen allt mer sönderkörd. Gentianan mitt mellan krafiga hjulspår.</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21876,13 +21865,13 @@
       <c r="AY189" t="inlineStr"/>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60980659</t>
+          <t>https://artportalen.se/Sighting/60980658</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>60980660</v>
+        <v>60980659</v>
       </c>
       <c r="B190" t="n">
         <v>106414</v>
@@ -21908,7 +21897,7 @@
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>64</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -21923,17 +21912,17 @@
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Ås Backen 10:1, kraftledning 830 m V om väg 745, Jmt</t>
+          <t>Ås Backen 11:1, kraftledning 700 m V om väg 745, Jmt</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>479598</v>
+        <v>479702</v>
       </c>
       <c r="R190" t="n">
-        <v>7019456</v>
+        <v>7019422</v>
       </c>
       <c r="S190" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -21967,7 +21956,7 @@
       </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>3 ex i blom inom 1 m2. Blå blommor. Längs serviceväg i kraftledning. Torrare del nedskuren i kulle. Nära Bakut på kartan.</t>
+          <t>64 ex i blom spridda längs 36 m serviceväg i kraftledning. Blå blommor. Torrare del nedskuren i kulle. Servicearbete pågår, men ännu har man inte nått denna del av vägen.</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21998,13 +21987,13 @@
       <c r="AY190" t="inlineStr"/>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60980660</t>
+          <t>https://artportalen.se/Sighting/60980659</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>60980661</v>
+        <v>60980660</v>
       </c>
       <c r="B191" t="n">
         <v>106414</v>
@@ -22030,7 +22019,7 @@
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -22045,14 +22034,14 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Ås Backen 10:1, kraftledning 840 m V om väg 745, Jmt</t>
+          <t>Ås Backen 10:1, kraftledning 830 m V om väg 745, Jmt</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>479584</v>
+        <v>479598</v>
       </c>
       <c r="R191" t="n">
-        <v>7019458</v>
+        <v>7019456</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -22089,7 +22078,7 @@
       </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>27 ex i blom inom 2x2 m. Blå blommor. Längs serviceväg i kraftledning. Torrare del nedskuren i kulle. Nära Bakut på kartan.</t>
+          <t>3 ex i blom inom 1 m2. Blå blommor. Längs serviceväg i kraftledning. Torrare del nedskuren i kulle. Nära Bakut på kartan.</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -22120,13 +22109,13 @@
       <c r="AY191" t="inlineStr"/>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60980661</t>
+          <t>https://artportalen.se/Sighting/60980660</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>68435013</v>
+        <v>60980661</v>
       </c>
       <c r="B192" t="n">
         <v>106414</v>
@@ -22152,7 +22141,7 @@
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -22160,16 +22149,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Ås-Backen 10:1, kraftledning 840 m V om väg 745, Jmt</t>
+          <t>Ås Backen 10:1, kraftledning 840 m V om väg 745, Jmt</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>479587</v>
+        <v>479584</v>
       </c>
       <c r="R192" t="n">
-        <v>7019456</v>
+        <v>7019458</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -22196,17 +22190,17 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2017-08-25</t>
+          <t>2016-08-13</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2017-08-25</t>
+          <t>2016-08-13</t>
         </is>
       </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>Detalj. Längs serviceväg i kraftledningsgata. 4 st längs 2 m vid den norra kanten av servicevägen.</t>
+          <t>27 ex i blom inom 2x2 m. Blå blommor. Längs serviceväg i kraftledning. Torrare del nedskuren i kulle. Nära Bakut på kartan.</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -22220,7 +22214,7 @@
       </c>
       <c r="AI192" t="inlineStr">
         <is>
-          <t>Serviceväg i kraftledningsgata, torrare del nedskuren i kulle</t>
+          <t>kraftledningsgata</t>
         </is>
       </c>
       <c r="AT192" t="inlineStr"/>
@@ -22237,13 +22231,13 @@
       <c r="AY192" t="inlineStr"/>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68435013</t>
+          <t>https://artportalen.se/Sighting/60980661</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>68435014</v>
+        <v>68435013</v>
       </c>
       <c r="B193" t="n">
         <v>106414</v>
@@ -22269,7 +22263,7 @@
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -22279,14 +22273,14 @@
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Ås-Backen 10:1, kraftledning 830 m V om väg 745, Jmt</t>
+          <t>Ås-Backen 10:1, kraftledning 840 m V om väg 745, Jmt</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>479597</v>
+        <v>479587</v>
       </c>
       <c r="R193" t="n">
-        <v>7019454</v>
+        <v>7019456</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22323,7 +22317,7 @@
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>Detalj. Längs serviceväg i kraftledningsgata. 1 stort exemplar vid den norra kanten av servicevägen.</t>
+          <t>Detalj. Längs serviceväg i kraftledningsgata. 4 st längs 2 m vid den norra kanten av servicevägen.</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22354,13 +22348,13 @@
       <c r="AY193" t="inlineStr"/>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68435014</t>
+          <t>https://artportalen.se/Sighting/68435013</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>68435015</v>
+        <v>68435014</v>
       </c>
       <c r="B194" t="n">
         <v>106414</v>
@@ -22386,7 +22380,7 @@
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -22396,14 +22390,14 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Ås-Backen 11:1, kraftledning 700 m V om väg 745, Jmt</t>
+          <t>Ås-Backen 10:1, kraftledning 830 m V om väg 745, Jmt</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>479686</v>
+        <v>479597</v>
       </c>
       <c r="R194" t="n">
-        <v>7019427</v>
+        <v>7019454</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22440,7 +22434,7 @@
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Detalj. Längs serviceväg i kraftledningsgata. 3 ex tillsammans i mittremsa.</t>
+          <t>Detalj. Längs serviceväg i kraftledningsgata. 1 stort exemplar vid den norra kanten av servicevägen.</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22471,13 +22465,13 @@
       <c r="AY194" t="inlineStr"/>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68435015</t>
+          <t>https://artportalen.se/Sighting/68435014</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>68435016</v>
+        <v>68435015</v>
       </c>
       <c r="B195" t="n">
         <v>106414</v>
@@ -22503,7 +22497,7 @@
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -22517,10 +22511,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>479703</v>
+        <v>479686</v>
       </c>
       <c r="R195" t="n">
-        <v>7019422</v>
+        <v>7019427</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22557,7 +22551,7 @@
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>Detalj. Längs serviceväg i kraftledningsgata. 8 ex längs 4 m mittremsa och kant.</t>
+          <t>Detalj. Längs serviceväg i kraftledningsgata. 3 ex tillsammans i mittremsa.</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22588,13 +22582,13 @@
       <c r="AY195" t="inlineStr"/>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68435016</t>
+          <t>https://artportalen.se/Sighting/68435015</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>68435017</v>
+        <v>68435016</v>
       </c>
       <c r="B196" t="n">
         <v>106414</v>
@@ -22634,10 +22628,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>479710</v>
+        <v>479703</v>
       </c>
       <c r="R196" t="n">
-        <v>7019419</v>
+        <v>7019422</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22674,7 +22668,7 @@
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>Detalj. Längs serviceväg i kraftledningsgata. 8 ex längs 1 m mittremsa.</t>
+          <t>Detalj. Längs serviceväg i kraftledningsgata. 8 ex längs 4 m mittremsa och kant.</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22705,13 +22699,13 @@
       <c r="AY196" t="inlineStr"/>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68435017</t>
+          <t>https://artportalen.se/Sighting/68435016</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>68435018</v>
+        <v>68435017</v>
       </c>
       <c r="B197" t="n">
         <v>106414</v>
@@ -22737,7 +22731,7 @@
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -22751,10 +22745,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>479715</v>
+        <v>479710</v>
       </c>
       <c r="R197" t="n">
-        <v>7019417</v>
+        <v>7019419</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22791,7 +22785,7 @@
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>Detalj. Längs serviceväg i kraftledningsgata. 1 ex vid kant.</t>
+          <t>Detalj. Längs serviceväg i kraftledningsgata. 8 ex längs 1 m mittremsa.</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22822,13 +22816,13 @@
       <c r="AY197" t="inlineStr"/>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68435018</t>
+          <t>https://artportalen.se/Sighting/68435017</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>68435019</v>
+        <v>68435018</v>
       </c>
       <c r="B198" t="n">
         <v>106414</v>
@@ -22864,14 +22858,14 @@
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Ås-Backen 11:1, kraftledning 660 m V om väg 745, Jmt</t>
+          <t>Ås-Backen 11:1, kraftledning 700 m V om väg 745, Jmt</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>479764</v>
+        <v>479715</v>
       </c>
       <c r="R198" t="n">
-        <v>7019407</v>
+        <v>7019417</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22908,7 +22902,7 @@
       </c>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>Detalj. Längs serviceväg i kraftledningsgata. 1 ex i mittremsa.</t>
+          <t>Detalj. Längs serviceväg i kraftledningsgata. 1 ex vid kant.</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22939,13 +22933,13 @@
       <c r="AY198" t="inlineStr"/>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68435019</t>
+          <t>https://artportalen.se/Sighting/68435018</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>68435086</v>
+        <v>68435019</v>
       </c>
       <c r="B199" t="n">
         <v>106414</v>
@@ -22971,7 +22965,7 @@
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -22981,17 +22975,17 @@
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Ås-Backen 11:1, kraftledning 700 m VNV väg 745, Jmt</t>
+          <t>Ås-Backen 11:1, kraftledning 660 m V om väg 745, Jmt</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>479716</v>
+        <v>479764</v>
       </c>
       <c r="R199" t="n">
-        <v>7019419</v>
+        <v>7019407</v>
       </c>
       <c r="S199" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -23013,24 +23007,19 @@
           <t>Ås</t>
         </is>
       </c>
-      <c r="X199" t="inlineStr">
-        <is>
-          <t>Z-Kro-0891</t>
-        </is>
-      </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2016-08-13</t>
+          <t>2017-08-25</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2016-08-13</t>
+          <t>2017-08-25</t>
         </is>
       </c>
       <c r="AC199" t="inlineStr">
         <is>
-          <t>65 plantor, i blom. Med blå och ljusblå blommor. Längs serviceväg i kraftledningsgata, torrare del nedskuren i kulle. Varav 64 st längs 35 m kring koordinat O1439328, N7022112, samt 1 st lite skild från övriga vid koordinat O1439369, N7022105. Detaljer även som separata fynduppgifter. Körspår från pågående servicearbete längs kraftledningen i den ostliga delen av lokalen.</t>
+          <t>Detalj. Längs serviceväg i kraftledningsgata. 1 ex i mittremsa.</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -23041,6 +23030,11 @@
       </c>
       <c r="AG199" t="b">
         <v>0</v>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>Serviceväg i kraftledningsgata, torrare del nedskuren i kulle</t>
+        </is>
       </c>
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
@@ -23053,20 +23047,16 @@
           <t>Lars-Åke Bäckström</t>
         </is>
       </c>
-      <c r="AY199" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY199" t="inlineStr"/>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68435086</t>
+          <t>https://artportalen.se/Sighting/68435019</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>68435087</v>
+        <v>68435086</v>
       </c>
       <c r="B200" t="n">
         <v>106414</v>
@@ -23092,7 +23082,7 @@
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -23102,17 +23092,17 @@
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Ås-Backen 10:1, kraftledning 840 m VNV väg 745, Jmt</t>
+          <t>Ås-Backen 11:1, kraftledning 700 m VNV väg 745, Jmt</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>479592</v>
+        <v>479716</v>
       </c>
       <c r="R200" t="n">
-        <v>7019456</v>
+        <v>7019419</v>
       </c>
       <c r="S200" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -23136,7 +23126,7 @@
       </c>
       <c r="X200" t="inlineStr">
         <is>
-          <t>Z-Kro-0890</t>
+          <t>Z-Kro-0891</t>
         </is>
       </c>
       <c r="Y200" t="inlineStr">
@@ -23151,7 +23141,7 @@
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>30 plantor, i blom. Alla med blå blommor. Längs serviceväg i kraftledningsgata, torrare del nedskuren i kulle. I två grupper. Dels 27 st inom 2x2 m vid koordinat O1439210, N7022150. Dels 3 st inom 1 m2 vid koordinat O1439224, N7022147. Detaljer även som separata fynduppgifter.</t>
+          <t>65 plantor, i blom. Med blå och ljusblå blommor. Längs serviceväg i kraftledningsgata, torrare del nedskuren i kulle. Varav 64 st längs 35 m kring koordinat O1439328, N7022112, samt 1 st lite skild från övriga vid koordinat O1439369, N7022105. Detaljer även som separata fynduppgifter. Körspår från pågående servicearbete längs kraftledningen i den ostliga delen av lokalen.</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -23181,13 +23171,13 @@
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68435087</t>
+          <t>https://artportalen.se/Sighting/68435086</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>111775915</v>
+        <v>68435087</v>
       </c>
       <c r="B201" t="n">
         <v>106414</v>
@@ -23213,7 +23203,7 @@
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -23221,24 +23211,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Ås-Backen 4:3, kraftledingsgata, Jmt</t>
+          <t>Ås-Backen 10:1, kraftledning 840 m VNV väg 745, Jmt</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>480143</v>
+        <v>479592</v>
       </c>
       <c r="R201" t="n">
-        <v>7019297</v>
+        <v>7019456</v>
       </c>
       <c r="S201" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -23260,19 +23245,24 @@
           <t>Ås</t>
         </is>
       </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>Z-Kro-0890</t>
+        </is>
+      </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2016-08-13</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2016-08-13</t>
         </is>
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>23 blommande plantor i en grupp. Alla med mörkt blå blommor. I norra kanten av stig/enkel väg i kraftledningsgata under korsning mellan kraftledningar. Ca 250 m VNV om väg 745.</t>
+          <t>30 plantor, i blom. Alla med blå blommor. Längs serviceväg i kraftledningsgata, torrare del nedskuren i kulle. I två grupper. Dels 27 st inom 2x2 m vid koordinat O1439210, N7022150. Dels 3 st inom 1 m2 vid koordinat O1439224, N7022147. Detaljer även som separata fynduppgifter.</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -23283,11 +23273,6 @@
       </c>
       <c r="AG201" t="b">
         <v>0</v>
-      </c>
-      <c r="AI201" t="inlineStr">
-        <is>
-          <t>Stig i kraftledningsgata</t>
-        </is>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
@@ -23300,16 +23285,20 @@
           <t>Lars-Åke Bäckström</t>
         </is>
       </c>
-      <c r="AY201" t="inlineStr"/>
+      <c r="AY201" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111775915</t>
+          <t>https://artportalen.se/Sighting/68435087</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>111776461</v>
+        <v>111775915</v>
       </c>
       <c r="B202" t="n">
         <v>106414</v>
@@ -23335,7 +23324,7 @@
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -23350,14 +23339,14 @@
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Ås-Backen 9:1, kraftledingsgata, Jmt</t>
+          <t>Ås-Backen 4:3, kraftledingsgata, Jmt</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>479874</v>
+        <v>480143</v>
       </c>
       <c r="R202" t="n">
-        <v>7019374</v>
+        <v>7019297</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -23394,7 +23383,7 @@
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>4 blommande plantor i en grupp. Alla med mörkt blå blommor. I norra kanten av stig/enkel väg i kraftledningsgata under kraftledning. Ca 550 m VNV om väg 745.</t>
+          <t>23 blommande plantor i en grupp. Alla med mörkt blå blommor. I norra kanten av stig/enkel väg i kraftledningsgata under korsning mellan kraftledningar. Ca 250 m VNV om väg 745.</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -23425,13 +23414,13 @@
       <c r="AY202" t="inlineStr"/>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111776461</t>
+          <t>https://artportalen.se/Sighting/111775915</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>113012032</v>
+        <v>111776461</v>
       </c>
       <c r="B203" t="n">
         <v>106414</v>
@@ -23457,19 +23446,29 @@
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Åsbacken, Jmt</t>
+          <t>Ås-Backen 9:1, kraftledingsgata, Jmt</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>479760</v>
+        <v>479874</v>
       </c>
       <c r="R203" t="n">
-        <v>7019410</v>
+        <v>7019374</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -23496,12 +23495,17 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>4 blommande plantor i en grupp. Alla med mörkt blå blommor. I norra kanten av stig/enkel väg i kraftledningsgata under kraftledning. Ca 550 m VNV om väg 745.</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -23512,28 +23516,33 @@
       </c>
       <c r="AG203" t="b">
         <v>0</v>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>Stig i kraftledningsgata</t>
+        </is>
       </c>
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113012032</t>
+          <t>https://artportalen.se/Sighting/111776461</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>113012049</v>
+        <v>113012032</v>
       </c>
       <c r="B204" t="n">
         <v>106414</v>
@@ -23559,7 +23568,7 @@
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
@@ -23568,10 +23577,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>479744</v>
+        <v>479760</v>
       </c>
       <c r="R204" t="n">
-        <v>7019407</v>
+        <v>7019410</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -23629,13 +23638,13 @@
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113012049</t>
+          <t>https://artportalen.se/Sighting/113012032</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>113012050</v>
+        <v>113012049</v>
       </c>
       <c r="B205" t="n">
         <v>106414</v>
@@ -23661,7 +23670,7 @@
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -23670,10 +23679,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>479738</v>
+        <v>479744</v>
       </c>
       <c r="R205" t="n">
-        <v>7019410</v>
+        <v>7019407</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23731,16 +23740,16 @@
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113012050</t>
+          <t>https://artportalen.se/Sighting/113012049</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>136177837</v>
+        <v>113012050</v>
       </c>
       <c r="B206" t="n">
-        <v>106606</v>
+        <v>106414</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23763,32 +23772,22 @@
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr">
         <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Bodstaden, Bodstaden, Jmt</t>
+          <t>Åsbacken, Jmt</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>480173</v>
+        <v>479738</v>
       </c>
       <c r="R206" t="n">
-        <v>7019225</v>
+        <v>7019410</v>
       </c>
       <c r="S206" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -23812,27 +23811,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="Z206" t="inlineStr">
-        <is>
-          <t>18:03</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AB206" t="inlineStr">
-        <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>Ca. Vid vändplan och ca 50 längs vägkanten in mot kraftledningen.</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -23847,65 +23831,75 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Måns Svensson</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136177837</t>
+          <t>https://artportalen.se/Sighting/113012050</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>60215815</v>
+        <v>136177837</v>
       </c>
       <c r="B207" t="n">
-        <v>97983</v>
+        <v>106607</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>221945</v>
+        <v>221447</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr"/>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Patronbodarna, kraftledningsgata, ca 550 m ONO om, ca 450 m väster om Sågbä, Jmt</t>
+          <t>Bodstaden, Bodstaden, Jmt</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>478044</v>
+        <v>480173</v>
       </c>
       <c r="R207" t="n">
-        <v>7019874</v>
+        <v>7019225</v>
       </c>
       <c r="S207" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -23924,22 +23918,32 @@
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>Rödön</t>
+          <t>Ås</t>
         </is>
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>1998-07-15</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>1998-07-15</t>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AC207" t="inlineStr">
         <is>
-          <t>På stig i sluttande torrbacke i kraftledningsgata</t>
+          <t>Ca. Vid vändplan och ca 50 längs vägkanten in mot kraftledningen.</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -23954,24 +23958,24 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Bengt Petterson</t>
+          <t>Alexander Hoffmann, Måns Svensson</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60215815</t>
+          <t>https://artportalen.se/Sighting/136177837</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>124867126</v>
+        <v>60215815</v>
       </c>
       <c r="B208" t="n">
         <v>97983</v>
@@ -24002,14 +24006,14 @@
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Bakut, Jmt</t>
+          <t>Patronbodarna, kraftledningsgata, ca 550 m ONO om, ca 450 m väster om Sågbä, Jmt</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>479811</v>
+        <v>478044</v>
       </c>
       <c r="R208" t="n">
-        <v>7019329</v>
+        <v>7019874</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -24031,17 +24035,22 @@
       </c>
       <c r="W208" t="inlineStr">
         <is>
-          <t>Ås</t>
+          <t>Rödön</t>
         </is>
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>1998-07-15</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2024-09-25</t>
+          <t>1998-07-15</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>På stig i sluttande torrbacke i kraftledningsgata</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -24056,24 +24065,24 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>August Alvtegen Lundgren</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>August Alvtegen Lundgren</t>
+          <t>Bengt Petterson</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124867126</t>
+          <t>https://artportalen.se/Sighting/60215815</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>124867127</v>
+        <v>124867126</v>
       </c>
       <c r="B209" t="n">
         <v>97983</v>
@@ -24111,7 +24120,7 @@
         <v>479811</v>
       </c>
       <c r="R209" t="n">
-        <v>7019325</v>
+        <v>7019329</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -24169,60 +24178,51 @@
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124867127</t>
+          <t>https://artportalen.se/Sighting/124867126</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>4540308</v>
+        <v>124867127</v>
       </c>
       <c r="B210" t="n">
-        <v>98050</v>
+        <v>97983</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>222112</v>
+        <v>221945</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Tängskogen: Kraftledningen Sakrisbodarna, Jmt</t>
+          <t>Bakut, Jmt</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>478956</v>
+        <v>479811</v>
       </c>
       <c r="R210" t="n">
-        <v>7019622</v>
+        <v>7019325</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -24249,17 +24249,12 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2010-07-04</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2010-07-04</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>Serviceväg i norra kraftledningsgatan. Inom 1x3 m på en kulle mllan kraftledningsstolpar. Lågväxt vegetation.</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -24270,38 +24265,28 @@
       </c>
       <c r="AG210" t="b">
         <v>0</v>
-      </c>
-      <c r="AH210" t="inlineStr">
-        <is>
-          <t>Ruderatmark</t>
-        </is>
-      </c>
-      <c r="AI210" t="inlineStr">
-        <is>
-          <t>Serviceväg i kraftledning</t>
-        </is>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>August Alvtegen Lundgren</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>August Alvtegen Lundgren</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4540308</t>
+          <t>https://artportalen.se/Sighting/124867127</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>60065072</v>
+        <v>4540308</v>
       </c>
       <c r="B211" t="n">
         <v>98050</v>
@@ -24329,20 +24314,29 @@
           <t>(L.) Sw.</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr"/>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Tängskogen, kraftledningsgata ca 100 m väster om Sågbäcken, ca 350 m öster , Jmt</t>
+          <t>Tängskogen: Kraftledningen Sakrisbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>478385</v>
+        <v>478956</v>
       </c>
       <c r="R211" t="n">
-        <v>7019768</v>
+        <v>7019622</v>
       </c>
       <c r="S211" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -24366,17 +24360,17 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2000-07-15</t>
+          <t>2010-07-04</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2000-07-15</t>
+          <t>2010-07-04</t>
         </is>
       </c>
       <c r="AC211" t="inlineStr">
         <is>
-          <t>Stig i kraftledningsgata, skoterled vintertid</t>
+          <t>Serviceväg i norra kraftledningsgatan. Inom 1x3 m på en kulle mllan kraftledningsstolpar. Lågväxt vegetation.</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -24387,28 +24381,38 @@
       </c>
       <c r="AG211" t="b">
         <v>0</v>
+      </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>Ruderatmark</t>
+        </is>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>Serviceväg i kraftledning</t>
+        </is>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Bengt Petterson</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60065072</t>
+          <t>https://artportalen.se/Sighting/4540308</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>60065073</v>
+        <v>60065072</v>
       </c>
       <c r="B212" t="n">
         <v>98050</v>
@@ -24439,14 +24443,14 @@
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Tängskogen, kraftledningsgata ca 100 m öster om stigen till Sakrisbodarna, , Jmt</t>
+          <t>Tängskogen, kraftledningsgata ca 100 m väster om Sågbäcken, ca 350 m öster , Jmt</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>479037</v>
+        <v>478385</v>
       </c>
       <c r="R212" t="n">
-        <v>7019576</v>
+        <v>7019768</v>
       </c>
       <c r="S212" t="n">
         <v>25</v>
@@ -24509,13 +24513,13 @@
       <c r="AY212" t="inlineStr"/>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60065073</t>
+          <t>https://artportalen.se/Sighting/60065072</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>60065074</v>
+        <v>60065073</v>
       </c>
       <c r="B213" t="n">
         <v>98050</v>
@@ -24546,14 +24550,14 @@
       <c r="I213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Tängskogen, kraftledningsgata ca 50 m väster om stigen till Sakrisbodarna, , Jmt</t>
+          <t>Tängskogen, kraftledningsgata ca 100 m öster om stigen till Sakrisbodarna, , Jmt</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>478907</v>
+        <v>479037</v>
       </c>
       <c r="R213" t="n">
-        <v>7019645</v>
+        <v>7019576</v>
       </c>
       <c r="S213" t="n">
         <v>25</v>
@@ -24616,13 +24620,13 @@
       <c r="AY213" t="inlineStr"/>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60065074</t>
+          <t>https://artportalen.se/Sighting/60065073</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>79447350</v>
+        <v>60065074</v>
       </c>
       <c r="B214" t="n">
         <v>98050</v>
@@ -24650,34 +24654,20 @@
           <t>(L.) Sw.</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t>bladfällning, vissnar</t>
-        </is>
-      </c>
+      <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Tängskogen: Kraftledningen 2, Jmt</t>
+          <t>Tängskogen, kraftledningsgata ca 50 m väster om stigen till Sakrisbodarna, , Jmt</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>478677</v>
+        <v>478907</v>
       </c>
       <c r="R214" t="n">
-        <v>7019703</v>
+        <v>7019645</v>
       </c>
       <c r="S214" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -24701,17 +24691,17 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2019-08-16</t>
+          <t>2000-07-15</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2019-08-16</t>
+          <t>2000-07-15</t>
         </is>
       </c>
       <c r="AC214" t="inlineStr">
         <is>
-          <t>3 plantor tillsammans i mittremsa på serviceväg i kraftledningsgata. Vissnande.</t>
+          <t>Stig i kraftledningsgata, skoterled vintertid</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24722,63 +24712,58 @@
       </c>
       <c r="AG214" t="b">
         <v>0</v>
-      </c>
-      <c r="AI214" t="inlineStr">
-        <is>
-          <t>Serviceväg i kraftledningsgata</t>
-        </is>
       </c>
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Bengt Petterson</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79447350</t>
+          <t>https://artportalen.se/Sighting/60065074</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>61231652</v>
+        <v>79447350</v>
       </c>
       <c r="B215" t="n">
-        <v>104628</v>
+        <v>98050</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>222412</v>
+        <v>222112</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Sw.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -24786,16 +24771,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>bladfällning, vissnar</t>
+        </is>
+      </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Tängskogen, Sågbäcken; södra delen, i kraftledningen,, Jmt</t>
+          <t>Tängskogen: Kraftledningen 2, Jmt</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>478491</v>
+        <v>478677</v>
       </c>
       <c r="R215" t="n">
-        <v>7019745</v>
+        <v>7019703</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24822,17 +24812,17 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2000-07-15</t>
+          <t>2019-08-16</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2000-07-15</t>
+          <t>2019-08-16</t>
         </is>
       </c>
       <c r="AC215" t="inlineStr">
         <is>
-          <t>Kraftledningsgata,</t>
+          <t>3 plantor tillsammans i mittremsa på serviceväg i kraftledningsgata. Vissnande.</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -24843,31 +24833,36 @@
       </c>
       <c r="AG215" t="b">
         <v>0</v>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>Serviceväg i kraftledningsgata</t>
+        </is>
       </c>
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Bengt Petterson</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61231652</t>
+          <t>https://artportalen.se/Sighting/79447350</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>86321926</v>
+        <v>61231652</v>
       </c>
       <c r="B216" t="n">
-        <v>99028</v>
+        <v>104628</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24875,41 +24870,46 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>223572</v>
+        <v>222412</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
-      <c r="K216" t="inlineStr"/>
-      <c r="L216" t="inlineStr"/>
-      <c r="N216" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Bakut, Jmt</t>
+          <t>Tängskogen, Sågbäcken; södra delen, i kraftledningen,, Jmt</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>479980</v>
+        <v>478491</v>
       </c>
       <c r="R216" t="n">
-        <v>7019566</v>
+        <v>7019745</v>
       </c>
       <c r="S216" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -24933,12 +24933,17 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2000-07-15</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2000-07-15</t>
+        </is>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>Kraftledningsgata,</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -24947,31 +24952,30 @@
       <c r="AE216" t="b">
         <v>0</v>
       </c>
-      <c r="AF216" t="inlineStr"/>
       <c r="AG216" t="b">
         <v>0</v>
       </c>
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Bengt Petterson</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86321926</t>
+          <t>https://artportalen.se/Sighting/61231652</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>86354226</v>
+        <v>86321926</v>
       </c>
       <c r="B217" t="n">
         <v>99028</v>
@@ -25010,10 +25014,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>479482</v>
+        <v>479980</v>
       </c>
       <c r="R217" t="n">
-        <v>7020672</v>
+        <v>7019566</v>
       </c>
       <c r="S217" t="n">
         <v>25</v>
@@ -25040,12 +25044,12 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2020-06-19</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2020-06-19</t>
+          <t>2020-06-17</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -25072,54 +25076,58 @@
       <c r="AY217" t="inlineStr"/>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86354226</t>
+          <t>https://artportalen.se/Sighting/86321926</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129389463</v>
+        <v>86354226</v>
       </c>
       <c r="B218" t="n">
-        <v>92208</v>
+        <v>99028</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>658</v>
+        <v>223572</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Rödflon-Åsbacken, Jmt</t>
+          <t>Bakut, Jmt</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>483403</v>
+        <v>479482</v>
       </c>
       <c r="R218" t="n">
-        <v>7018348</v>
+        <v>7020672</v>
       </c>
       <c r="S218" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -25143,12 +25151,12 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2020-06-19</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2020-06-19</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -25157,30 +25165,31 @@
       <c r="AE218" t="b">
         <v>0</v>
       </c>
+      <c r="AF218" t="inlineStr"/>
       <c r="AG218" t="b">
         <v>0</v>
       </c>
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129389463</t>
+          <t>https://artportalen.se/Sighting/86354226</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129389470</v>
+        <v>129389463</v>
       </c>
       <c r="B219" t="n">
         <v>92208</v>
@@ -25215,10 +25224,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>483547</v>
+        <v>483403</v>
       </c>
       <c r="R219" t="n">
-        <v>7018301</v>
+        <v>7018348</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -25276,13 +25285,13 @@
       <c r="AY219" t="inlineStr"/>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129389470</t>
+          <t>https://artportalen.se/Sighting/129389463</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129389493</v>
+        <v>129389470</v>
       </c>
       <c r="B220" t="n">
         <v>92208</v>
@@ -25317,10 +25326,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>483523</v>
+        <v>483547</v>
       </c>
       <c r="R220" t="n">
-        <v>7018321</v>
+        <v>7018301</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -25378,51 +25387,51 @@
       <c r="AY220" t="inlineStr"/>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129389493</t>
+          <t>https://artportalen.se/Sighting/129389470</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>120305508</v>
+        <v>129389493</v>
       </c>
       <c r="B221" t="n">
-        <v>89029</v>
+        <v>92208</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>4392</v>
+        <v>658</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Ängsvaxing agg.</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Cuphophyllus pratensis s.lat.</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr"/>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Kallkas, Jmt</t>
+          <t>Rödflon-Åsbacken, Jmt</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>483535</v>
+        <v>483523</v>
       </c>
       <c r="R221" t="n">
-        <v>7018383</v>
+        <v>7018321</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -25449,12 +25458,12 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -25469,27 +25478,27 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg, Lars-Olof Grund</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305508</t>
+          <t>https://artportalen.se/Sighting/129389493</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>120305099</v>
+        <v>120305508</v>
       </c>
       <c r="B222" t="n">
-        <v>89035</v>
+        <v>89029</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -25497,16 +25506,16 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>4398</v>
+        <v>4392</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Vitvaxing agg.</t>
+          <t>Ängsvaxing agg.</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Cuphophyllus virgineus s.lat.</t>
+          <t>Cuphophyllus pratensis s.lat.</t>
         </is>
       </c>
       <c r="H222" t="inlineStr"/>
@@ -25521,10 +25530,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>483128</v>
+        <v>483535</v>
       </c>
       <c r="R222" t="n">
-        <v>7018500</v>
+        <v>7018383</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25551,12 +25560,12 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -25576,19 +25585,19 @@
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg, Lars-Olof Grund</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305099</t>
+          <t>https://artportalen.se/Sighting/120305508</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>120305515</v>
+        <v>120305099</v>
       </c>
       <c r="B223" t="n">
         <v>89035</v>
@@ -25623,10 +25632,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>483563</v>
+        <v>483128</v>
       </c>
       <c r="R223" t="n">
-        <v>7018375</v>
+        <v>7018500</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25653,12 +25662,12 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -25678,19 +25687,19 @@
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg, Lars-Olof Grund</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305515</t>
+          <t>https://artportalen.se/Sighting/120305099</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>120305516</v>
+        <v>120305515</v>
       </c>
       <c r="B224" t="n">
         <v>89035</v>
@@ -25725,10 +25734,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>483674</v>
+        <v>483563</v>
       </c>
       <c r="R224" t="n">
-        <v>7018345</v>
+        <v>7018375</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25786,13 +25795,13 @@
       <c r="AY224" t="inlineStr"/>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305516</t>
+          <t>https://artportalen.se/Sighting/120305515</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>120305517</v>
+        <v>120305516</v>
       </c>
       <c r="B225" t="n">
         <v>89035</v>
@@ -25827,10 +25836,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>483718</v>
+        <v>483674</v>
       </c>
       <c r="R225" t="n">
-        <v>7018333</v>
+        <v>7018345</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25888,13 +25897,13 @@
       <c r="AY225" t="inlineStr"/>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305517</t>
+          <t>https://artportalen.se/Sighting/120305516</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>120305518</v>
+        <v>120305517</v>
       </c>
       <c r="B226" t="n">
         <v>89035</v>
@@ -25929,10 +25938,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>484082</v>
+        <v>483718</v>
       </c>
       <c r="R226" t="n">
-        <v>7018230</v>
+        <v>7018333</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25990,51 +25999,51 @@
       <c r="AY226" t="inlineStr"/>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305518</t>
+          <t>https://artportalen.se/Sighting/120305517</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129389473</v>
+        <v>120305518</v>
       </c>
       <c r="B227" t="n">
-        <v>79327</v>
+        <v>89035</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6425</v>
+        <v>4398</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitvaxing agg.</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr"/>
+          <t>Cuphophyllus virgineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Rödflon-Åsbacken, Jmt</t>
+          <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>483590</v>
+        <v>484082</v>
       </c>
       <c r="R227" t="n">
-        <v>7018296</v>
+        <v>7018230</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -26061,12 +26070,12 @@
       </c>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -26081,65 +26090,65 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg, Lars-Olof Grund</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129389473</t>
+          <t>https://artportalen.se/Sighting/120305518</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>117831415</v>
+        <v>129389473</v>
       </c>
       <c r="B228" t="n">
-        <v>41670</v>
+        <v>79327</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100453</v>
+        <v>6425</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Trolldruvemätare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Baptria tibiale</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Esper, 1790)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Bergtorpet, Bergtorpet, Jmt</t>
+          <t>Rödflon-Åsbacken, Jmt</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>487279</v>
+        <v>483590</v>
       </c>
       <c r="R228" t="n">
-        <v>7017311</v>
+        <v>7018296</v>
       </c>
       <c r="S228" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -26148,7 +26157,7 @@
       </c>
       <c r="U228" t="inlineStr">
         <is>
-          <t>Östersund</t>
+          <t>Krokom</t>
         </is>
       </c>
       <c r="V228" t="inlineStr">
@@ -26158,17 +26167,17 @@
       </c>
       <c r="W228" t="inlineStr">
         <is>
-          <t>Lit</t>
+          <t>Ås</t>
         </is>
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -26183,68 +26192,65 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Jonny Daborg</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117831415</t>
+          <t>https://artportalen.se/Sighting/129389473</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>94446445</v>
+        <v>117831415</v>
       </c>
       <c r="B229" t="n">
-        <v>43249</v>
+        <v>41670</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>101248</v>
+        <v>100453</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Violett guldvinge</t>
+          <t>Trolldruvemätare</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Lycaena helle</t>
+          <t>Baptria tibiale</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Esper, 1790)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
-      <c r="K229" t="inlineStr"/>
-      <c r="L229" t="inlineStr"/>
-      <c r="M229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Östersund, Jmt</t>
+          <t>Bergtorpet, Bergtorpet, Jmt</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>486122</v>
+        <v>487279</v>
       </c>
       <c r="R229" t="n">
-        <v>7017672</v>
+        <v>7017311</v>
       </c>
       <c r="S229" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -26253,7 +26259,7 @@
       </c>
       <c r="U229" t="inlineStr">
         <is>
-          <t>Krokom</t>
+          <t>Östersund</t>
         </is>
       </c>
       <c r="V229" t="inlineStr">
@@ -26263,17 +26269,17 @@
       </c>
       <c r="W229" t="inlineStr">
         <is>
-          <t>Ås</t>
+          <t>Lit</t>
         </is>
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -26288,24 +26294,24 @@
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Rashid Kadhim, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94446445</t>
+          <t>https://artportalen.se/Sighting/117831415</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>120305839</v>
+        <v>94446445</v>
       </c>
       <c r="B230" t="n">
         <v>43249</v>
@@ -26333,24 +26339,23 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I230" t="inlineStr"/>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
+      <c r="M230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Kallkas, Jmt</t>
+          <t>Östersund, Jmt</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>483464</v>
+        <v>486122</v>
       </c>
       <c r="R230" t="n">
-        <v>7018400</v>
+        <v>7017672</v>
       </c>
       <c r="S230" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -26374,12 +26379,12 @@
       </c>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -26394,24 +26399,24 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305839</t>
+          <t>https://artportalen.se/Sighting/94446445</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>120305840</v>
+        <v>120305839</v>
       </c>
       <c r="B231" t="n">
         <v>43249</v>
@@ -26450,10 +26455,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>483667</v>
+        <v>483464</v>
       </c>
       <c r="R231" t="n">
-        <v>7018345</v>
+        <v>7018400</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -26511,13 +26516,13 @@
       <c r="AY231" t="inlineStr"/>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305840</t>
+          <t>https://artportalen.se/Sighting/120305839</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>120305841</v>
+        <v>120305840</v>
       </c>
       <c r="B232" t="n">
         <v>43249</v>
@@ -26556,10 +26561,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>484128</v>
+        <v>483667</v>
       </c>
       <c r="R232" t="n">
-        <v>7018221</v>
+        <v>7018345</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -26617,13 +26622,13 @@
       <c r="AY232" t="inlineStr"/>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305841</t>
+          <t>https://artportalen.se/Sighting/120305840</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>120305862</v>
+        <v>120305841</v>
       </c>
       <c r="B233" t="n">
         <v>43249</v>
@@ -26662,10 +26667,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>482982</v>
+        <v>484128</v>
       </c>
       <c r="R233" t="n">
-        <v>7018499</v>
+        <v>7018221</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -26723,13 +26728,13 @@
       <c r="AY233" t="inlineStr"/>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305862</t>
+          <t>https://artportalen.se/Sighting/120305841</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>120305863</v>
+        <v>120305862</v>
       </c>
       <c r="B234" t="n">
         <v>43249</v>
@@ -26768,10 +26773,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>482991</v>
+        <v>482982</v>
       </c>
       <c r="R234" t="n">
-        <v>7018539</v>
+        <v>7018499</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -26829,13 +26834,13 @@
       <c r="AY234" t="inlineStr"/>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305863</t>
+          <t>https://artportalen.se/Sighting/120305862</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>120305864</v>
+        <v>120305863</v>
       </c>
       <c r="B235" t="n">
         <v>43249</v>
@@ -26874,10 +26879,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>483245</v>
+        <v>482991</v>
       </c>
       <c r="R235" t="n">
-        <v>7018462</v>
+        <v>7018539</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -26935,13 +26940,13 @@
       <c r="AY235" t="inlineStr"/>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305864</t>
+          <t>https://artportalen.se/Sighting/120305863</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>120306052</v>
+        <v>120305864</v>
       </c>
       <c r="B236" t="n">
         <v>43249</v>
@@ -26980,10 +26985,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>483825</v>
+        <v>483245</v>
       </c>
       <c r="R236" t="n">
-        <v>7018304</v>
+        <v>7018462</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -27018,11 +27023,6 @@
           <t>2024-06-18</t>
         </is>
       </c>
-      <c r="AC236" t="inlineStr">
-        <is>
-          <t>Ägg</t>
-        </is>
-      </c>
       <c r="AD236" t="b">
         <v>0</v>
       </c>
@@ -27046,13 +27046,13 @@
       <c r="AY236" t="inlineStr"/>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120306052</t>
+          <t>https://artportalen.se/Sighting/120305864</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>120306054</v>
+        <v>120306052</v>
       </c>
       <c r="B237" t="n">
         <v>43249</v>
@@ -27091,10 +27091,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>484194</v>
+        <v>483825</v>
       </c>
       <c r="R237" t="n">
-        <v>7018204</v>
+        <v>7018304</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -27157,38 +27157,38 @@
       <c r="AY237" t="inlineStr"/>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120306054</t>
+          <t>https://artportalen.se/Sighting/120306052</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>120305975</v>
+        <v>120306054</v>
       </c>
       <c r="B238" t="n">
-        <v>99017</v>
+        <v>43249</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>219795</v>
+        <v>101248</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Violett guldvinge</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Lycaena helle</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -27202,10 +27202,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>483124</v>
+        <v>484194</v>
       </c>
       <c r="R238" t="n">
-        <v>7018464</v>
+        <v>7018204</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -27240,6 +27240,11 @@
           <t>2024-06-18</t>
         </is>
       </c>
+      <c r="AC238" t="inlineStr">
+        <is>
+          <t>Ägg</t>
+        </is>
+      </c>
       <c r="AD238" t="b">
         <v>0</v>
       </c>
@@ -27263,63 +27268,58 @@
       <c r="AY238" t="inlineStr"/>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305975</t>
+          <t>https://artportalen.se/Sighting/120306054</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>4540065</v>
+        <v>120305975</v>
       </c>
       <c r="B239" t="n">
-        <v>98050</v>
+        <v>99017</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>222112</v>
+        <v>219795</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J239" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Granbo, kraftledning, Jmt</t>
+          <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>481772</v>
+        <v>483124</v>
       </c>
       <c r="R239" t="n">
-        <v>7018859</v>
+        <v>7018464</v>
       </c>
       <c r="S239" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -27343,17 +27343,12 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>2010-07-01</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2010-07-01</t>
-        </is>
-      </c>
-      <c r="AC239" t="inlineStr">
-        <is>
-          <t>Serviceväg i norra kraftledningsgatan. Längs 30 m på en kulle med lågväxt vegetation. Berg i dagen.</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -27364,38 +27359,28 @@
       </c>
       <c r="AG239" t="b">
         <v>0</v>
-      </c>
-      <c r="AH239" t="inlineStr">
-        <is>
-          <t>Ruderatmark</t>
-        </is>
-      </c>
-      <c r="AI239" t="inlineStr">
-        <is>
-          <t>Serviceväg i kraftledning</t>
-        </is>
       </c>
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4540065</t>
+          <t>https://artportalen.se/Sighting/120305975</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>120305933</v>
+        <v>4540065</v>
       </c>
       <c r="B240" t="n">
         <v>98050</v>
@@ -27425,22 +27410,27 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Kallkas, Jmt</t>
+          <t>Granbo, kraftledning, Jmt</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>483401</v>
+        <v>481772</v>
       </c>
       <c r="R240" t="n">
-        <v>7018418</v>
+        <v>7018859</v>
       </c>
       <c r="S240" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -27464,12 +27454,17 @@
       </c>
       <c r="Y240" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2010-07-01</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2010-07-01</t>
+        </is>
+      </c>
+      <c r="AC240" t="inlineStr">
+        <is>
+          <t>Serviceväg i norra kraftledningsgatan. Längs 30 m på en kulle med lågväxt vegetation. Berg i dagen.</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -27480,28 +27475,38 @@
       </c>
       <c r="AG240" t="b">
         <v>0</v>
+      </c>
+      <c r="AH240" t="inlineStr">
+        <is>
+          <t>Ruderatmark</t>
+        </is>
+      </c>
+      <c r="AI240" t="inlineStr">
+        <is>
+          <t>Serviceväg i kraftledning</t>
+        </is>
       </c>
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305933</t>
+          <t>https://artportalen.se/Sighting/4540065</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>120305934</v>
+        <v>120305933</v>
       </c>
       <c r="B241" t="n">
         <v>98050</v>
@@ -27540,10 +27545,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>483408</v>
+        <v>483401</v>
       </c>
       <c r="R241" t="n">
-        <v>7018417</v>
+        <v>7018418</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27601,13 +27606,13 @@
       <c r="AY241" t="inlineStr"/>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305934</t>
+          <t>https://artportalen.se/Sighting/120305933</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>120305935</v>
+        <v>120305934</v>
       </c>
       <c r="B242" t="n">
         <v>98050</v>
@@ -27646,10 +27651,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>483409</v>
+        <v>483408</v>
       </c>
       <c r="R242" t="n">
-        <v>7018416</v>
+        <v>7018417</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -27707,13 +27712,13 @@
       <c r="AY242" t="inlineStr"/>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305935</t>
+          <t>https://artportalen.se/Sighting/120305934</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>120305936</v>
+        <v>120305935</v>
       </c>
       <c r="B243" t="n">
         <v>98050</v>
@@ -27752,10 +27757,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>483420</v>
+        <v>483409</v>
       </c>
       <c r="R243" t="n">
-        <v>7018413</v>
+        <v>7018416</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27813,13 +27818,13 @@
       <c r="AY243" t="inlineStr"/>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305936</t>
+          <t>https://artportalen.se/Sighting/120305935</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>120305939</v>
+        <v>120305936</v>
       </c>
       <c r="B244" t="n">
         <v>98050</v>
@@ -27858,10 +27863,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>483454</v>
+        <v>483420</v>
       </c>
       <c r="R244" t="n">
-        <v>7018401</v>
+        <v>7018413</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -27919,13 +27924,13 @@
       <c r="AY244" t="inlineStr"/>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305939</t>
+          <t>https://artportalen.se/Sighting/120305936</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>120305941</v>
+        <v>120305939</v>
       </c>
       <c r="B245" t="n">
         <v>98050</v>
@@ -27964,10 +27969,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>483627</v>
+        <v>483454</v>
       </c>
       <c r="R245" t="n">
-        <v>7018355</v>
+        <v>7018401</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -28025,13 +28030,13 @@
       <c r="AY245" t="inlineStr"/>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305941</t>
+          <t>https://artportalen.se/Sighting/120305939</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>120305942</v>
+        <v>120305941</v>
       </c>
       <c r="B246" t="n">
         <v>98050</v>
@@ -28070,10 +28075,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>482978</v>
+        <v>483627</v>
       </c>
       <c r="R246" t="n">
-        <v>7018541</v>
+        <v>7018355</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -28131,13 +28136,13 @@
       <c r="AY246" t="inlineStr"/>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305942</t>
+          <t>https://artportalen.se/Sighting/120305941</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>120305943</v>
+        <v>120305942</v>
       </c>
       <c r="B247" t="n">
         <v>98050</v>
@@ -28176,10 +28181,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>483017</v>
+        <v>482978</v>
       </c>
       <c r="R247" t="n">
-        <v>7018528</v>
+        <v>7018541</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -28237,13 +28242,13 @@
       <c r="AY247" t="inlineStr"/>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305943</t>
+          <t>https://artportalen.se/Sighting/120305942</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>120305944</v>
+        <v>120305943</v>
       </c>
       <c r="B248" t="n">
         <v>98050</v>
@@ -28282,10 +28287,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>483121</v>
+        <v>483017</v>
       </c>
       <c r="R248" t="n">
-        <v>7018502</v>
+        <v>7018528</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -28343,13 +28348,13 @@
       <c r="AY248" t="inlineStr"/>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305944</t>
+          <t>https://artportalen.se/Sighting/120305943</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>120305945</v>
+        <v>120305944</v>
       </c>
       <c r="B249" t="n">
         <v>98050</v>
@@ -28388,10 +28393,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>483152</v>
+        <v>483121</v>
       </c>
       <c r="R249" t="n">
-        <v>7018495</v>
+        <v>7018502</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -28449,13 +28454,13 @@
       <c r="AY249" t="inlineStr"/>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305945</t>
+          <t>https://artportalen.se/Sighting/120305944</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>120305947</v>
+        <v>120305945</v>
       </c>
       <c r="B250" t="n">
         <v>98050</v>
@@ -28494,10 +28499,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>483247</v>
+        <v>483152</v>
       </c>
       <c r="R250" t="n">
-        <v>7018461</v>
+        <v>7018495</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -28555,13 +28560,13 @@
       <c r="AY250" t="inlineStr"/>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305947</t>
+          <t>https://artportalen.se/Sighting/120305945</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>120305948</v>
+        <v>120305947</v>
       </c>
       <c r="B251" t="n">
         <v>98050</v>
@@ -28600,10 +28605,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>483254</v>
+        <v>483247</v>
       </c>
       <c r="R251" t="n">
-        <v>7018459</v>
+        <v>7018461</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -28661,13 +28666,13 @@
       <c r="AY251" t="inlineStr"/>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305948</t>
+          <t>https://artportalen.se/Sighting/120305947</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>120305949</v>
+        <v>120305948</v>
       </c>
       <c r="B252" t="n">
         <v>98050</v>
@@ -28706,10 +28711,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>483272</v>
+        <v>483254</v>
       </c>
       <c r="R252" t="n">
-        <v>7018454</v>
+        <v>7018459</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -28767,13 +28772,13 @@
       <c r="AY252" t="inlineStr"/>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305949</t>
+          <t>https://artportalen.se/Sighting/120305948</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>120305950</v>
+        <v>120305949</v>
       </c>
       <c r="B253" t="n">
         <v>98050</v>
@@ -28812,10 +28817,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>483290</v>
+        <v>483272</v>
       </c>
       <c r="R253" t="n">
-        <v>7018440</v>
+        <v>7018454</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28873,13 +28878,13 @@
       <c r="AY253" t="inlineStr"/>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305950</t>
+          <t>https://artportalen.se/Sighting/120305949</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>120305952</v>
+        <v>120305950</v>
       </c>
       <c r="B254" t="n">
         <v>98050</v>
@@ -28918,10 +28923,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>483300</v>
+        <v>483290</v>
       </c>
       <c r="R254" t="n">
-        <v>7018430</v>
+        <v>7018440</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -28979,13 +28984,13 @@
       <c r="AY254" t="inlineStr"/>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305952</t>
+          <t>https://artportalen.se/Sighting/120305950</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>120305953</v>
+        <v>120305952</v>
       </c>
       <c r="B255" t="n">
         <v>98050</v>
@@ -29024,10 +29029,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>483310</v>
+        <v>483300</v>
       </c>
       <c r="R255" t="n">
-        <v>7018423</v>
+        <v>7018430</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -29085,13 +29090,13 @@
       <c r="AY255" t="inlineStr"/>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305953</t>
+          <t>https://artportalen.se/Sighting/120305952</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>120305954</v>
+        <v>120305953</v>
       </c>
       <c r="B256" t="n">
         <v>98050</v>
@@ -29130,10 +29135,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>483314</v>
+        <v>483310</v>
       </c>
       <c r="R256" t="n">
-        <v>7018420</v>
+        <v>7018423</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -29191,13 +29196,13 @@
       <c r="AY256" t="inlineStr"/>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305954</t>
+          <t>https://artportalen.se/Sighting/120305953</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>120305955</v>
+        <v>120305954</v>
       </c>
       <c r="B257" t="n">
         <v>98050</v>
@@ -29236,10 +29241,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>483318</v>
+        <v>483314</v>
       </c>
       <c r="R257" t="n">
-        <v>7018419</v>
+        <v>7018420</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -29297,13 +29302,13 @@
       <c r="AY257" t="inlineStr"/>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305955</t>
+          <t>https://artportalen.se/Sighting/120305954</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>120305956</v>
+        <v>120305955</v>
       </c>
       <c r="B258" t="n">
         <v>98050</v>
@@ -29342,10 +29347,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>483335</v>
+        <v>483318</v>
       </c>
       <c r="R258" t="n">
-        <v>7018407</v>
+        <v>7018419</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -29403,38 +29408,38 @@
       <c r="AY258" t="inlineStr"/>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120305956</t>
+          <t>https://artportalen.se/Sighting/120305955</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>120306033</v>
+        <v>120305956</v>
       </c>
       <c r="B259" t="n">
-        <v>101326</v>
+        <v>98050</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>222498</v>
+        <v>222112</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Sw.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -29448,10 +29453,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>483417</v>
+        <v>483335</v>
       </c>
       <c r="R259" t="n">
-        <v>7018414</v>
+        <v>7018407</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -29509,16 +29514,16 @@
       <c r="AY259" t="inlineStr"/>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120306033</t>
+          <t>https://artportalen.se/Sighting/120305956</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>129389502</v>
+        <v>120306033</v>
       </c>
       <c r="B260" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -29543,17 +29548,21 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I260" t="inlineStr"/>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Rödflon-Åsbacken, Jmt</t>
+          <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>483482</v>
+        <v>483417</v>
       </c>
       <c r="R260" t="n">
-        <v>7018331</v>
+        <v>7018414</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -29580,12 +29589,12 @@
       </c>
       <c r="Y260" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -29600,27 +29609,27 @@
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129389502</t>
+          <t>https://artportalen.se/Sighting/120306033</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>111909859</v>
+        <v>129389502</v>
       </c>
       <c r="B261" t="n">
-        <v>101228</v>
+        <v>101325</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -29628,34 +29637,34 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
-          <t>Halåsen, NV om Åsmundgårdstjärnen, Jmt</t>
+          <t>Rödflon-Åsbacken, Jmt</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>487232</v>
+        <v>483482</v>
       </c>
       <c r="R261" t="n">
-        <v>7017303</v>
+        <v>7018331</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -29667,7 +29676,7 @@
       </c>
       <c r="U261" t="inlineStr">
         <is>
-          <t>Östersund</t>
+          <t>Krokom</t>
         </is>
       </c>
       <c r="V261" t="inlineStr">
@@ -29677,17 +29686,17 @@
       </c>
       <c r="W261" t="inlineStr">
         <is>
-          <t>Lit</t>
+          <t>Ås</t>
         </is>
       </c>
       <c r="Y261" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -29702,31 +29711,27 @@
       <c r="AT261" t="inlineStr"/>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Thomas Stålhandske</t>
-        </is>
-      </c>
-      <c r="AY261" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
-        </is>
-      </c>
+          <t>August Alvtegen</t>
+        </is>
+      </c>
+      <c r="AY261" t="inlineStr"/>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111909859</t>
+          <t>https://artportalen.se/Sighting/129389502</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>94446308</v>
+        <v>111909859</v>
       </c>
       <c r="B262" t="n">
-        <v>99028</v>
+        <v>101228</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -29734,43 +29739,37 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>223572</v>
+        <v>222771</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
-        </is>
-      </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr"/>
-      <c r="L262" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Östersund, Jmt</t>
+          <t>Halåsen, NV om Åsmundgårdstjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>486220</v>
+        <v>487232</v>
       </c>
       <c r="R262" t="n">
-        <v>7017668</v>
+        <v>7017303</v>
       </c>
       <c r="S262" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T262" t="inlineStr">
         <is>
@@ -29779,7 +29778,7 @@
       </c>
       <c r="U262" t="inlineStr">
         <is>
-          <t>Krokom</t>
+          <t>Östersund</t>
         </is>
       </c>
       <c r="V262" t="inlineStr">
@@ -29789,17 +29788,17 @@
       </c>
       <c r="W262" t="inlineStr">
         <is>
-          <t>Ås</t>
+          <t>Lit</t>
         </is>
       </c>
       <c r="Y262" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
         <is>
-          <t>2021-06-24</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -29814,24 +29813,28 @@
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Thomas Stålhandske</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY262" t="inlineStr"/>
+          <t>Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AY262" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
+        </is>
+      </c>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94446308</t>
+          <t>https://artportalen.se/Sighting/111909859</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>94446527</v>
+        <v>94446308</v>
       </c>
       <c r="B263" t="n">
         <v>99028</v>
@@ -29859,7 +29862,11 @@
           <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
-      <c r="I263" t="inlineStr"/>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K263" t="inlineStr"/>
       <c r="L263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
@@ -29868,10 +29875,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>485984</v>
+        <v>486220</v>
       </c>
       <c r="R263" t="n">
-        <v>7017704</v>
+        <v>7017668</v>
       </c>
       <c r="S263" t="n">
         <v>25</v>
@@ -29929,56 +29936,53 @@
       <c r="AY263" t="inlineStr"/>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94446527</t>
+          <t>https://artportalen.se/Sighting/94446308</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>86410369</v>
+        <v>94446527</v>
       </c>
       <c r="B264" t="n">
-        <v>43249</v>
+        <v>99028</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>101248</v>
+        <v>223572</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Violett guldvinge</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Lycaena helle</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
-      <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr"/>
-      <c r="M264" t="inlineStr"/>
-      <c r="N264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
         <is>
-          <t>Bye, Jmt</t>
+          <t>Östersund, Jmt</t>
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>492790</v>
+        <v>485984</v>
       </c>
       <c r="R264" t="n">
-        <v>7015849</v>
+        <v>7017704</v>
       </c>
       <c r="S264" t="n">
         <v>25</v>
@@ -29990,7 +29994,7 @@
       </c>
       <c r="U264" t="inlineStr">
         <is>
-          <t>Östersund</t>
+          <t>Krokom</t>
         </is>
       </c>
       <c r="V264" t="inlineStr">
@@ -30000,17 +30004,17 @@
       </c>
       <c r="W264" t="inlineStr">
         <is>
-          <t>Lit</t>
+          <t>Ås</t>
         </is>
       </c>
       <c r="Y264" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="AD264" t="b">
@@ -30019,7 +30023,6 @@
       <c r="AE264" t="b">
         <v>0</v>
       </c>
-      <c r="AF264" t="inlineStr"/>
       <c r="AG264" t="b">
         <v>0</v>
       </c>
@@ -30037,13 +30040,13 @@
       <c r="AY264" t="inlineStr"/>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86410369</t>
+          <t>https://artportalen.se/Sighting/94446527</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>86410388</v>
+        <v>86410369</v>
       </c>
       <c r="B265" t="n">
         <v>43249</v>
@@ -30083,10 +30086,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>492662</v>
+        <v>492790</v>
       </c>
       <c r="R265" t="n">
-        <v>7015909</v>
+        <v>7015849</v>
       </c>
       <c r="S265" t="n">
         <v>25</v>
@@ -30145,13 +30148,13 @@
       <c r="AY265" t="inlineStr"/>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86410388</t>
+          <t>https://artportalen.se/Sighting/86410369</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>86410413</v>
+        <v>86410388</v>
       </c>
       <c r="B266" t="n">
         <v>43249</v>
@@ -30191,10 +30194,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>492403</v>
+        <v>492662</v>
       </c>
       <c r="R266" t="n">
-        <v>7015977</v>
+        <v>7015909</v>
       </c>
       <c r="S266" t="n">
         <v>25</v>
@@ -30253,13 +30256,13 @@
       <c r="AY266" t="inlineStr"/>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86410413</t>
+          <t>https://artportalen.se/Sighting/86410388</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>86410432</v>
+        <v>86410413</v>
       </c>
       <c r="B267" t="n">
         <v>43249</v>
@@ -30299,10 +30302,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>492360</v>
+        <v>492403</v>
       </c>
       <c r="R267" t="n">
-        <v>7015989</v>
+        <v>7015977</v>
       </c>
       <c r="S267" t="n">
         <v>25</v>
@@ -30361,13 +30364,13 @@
       <c r="AY267" t="inlineStr"/>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86410432</t>
+          <t>https://artportalen.se/Sighting/86410413</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>86410459</v>
+        <v>86410432</v>
       </c>
       <c r="B268" t="n">
         <v>43249</v>
@@ -30407,10 +30410,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>492179</v>
+        <v>492360</v>
       </c>
       <c r="R268" t="n">
-        <v>7016036</v>
+        <v>7015989</v>
       </c>
       <c r="S268" t="n">
         <v>25</v>
@@ -30469,13 +30472,13 @@
       <c r="AY268" t="inlineStr"/>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86410459</t>
+          <t>https://artportalen.se/Sighting/86410432</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>86410475</v>
+        <v>86410459</v>
       </c>
       <c r="B269" t="n">
         <v>43249</v>
@@ -30515,10 +30518,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>491884</v>
+        <v>492179</v>
       </c>
       <c r="R269" t="n">
-        <v>7016127</v>
+        <v>7016036</v>
       </c>
       <c r="S269" t="n">
         <v>25</v>
@@ -30577,13 +30580,13 @@
       <c r="AY269" t="inlineStr"/>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86410475</t>
+          <t>https://artportalen.se/Sighting/86410459</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>86410497</v>
+        <v>86410475</v>
       </c>
       <c r="B270" t="n">
         <v>43249</v>
@@ -30611,11 +30614,7 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I270" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I270" t="inlineStr"/>
       <c r="J270" t="inlineStr"/>
       <c r="K270" t="inlineStr"/>
       <c r="L270" t="inlineStr"/>
@@ -30627,10 +30626,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>491757</v>
+        <v>491884</v>
       </c>
       <c r="R270" t="n">
-        <v>7016157</v>
+        <v>7016127</v>
       </c>
       <c r="S270" t="n">
         <v>25</v>
@@ -30689,13 +30688,13 @@
       <c r="AY270" t="inlineStr"/>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86410497</t>
+          <t>https://artportalen.se/Sighting/86410475</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>86410510</v>
+        <v>86410497</v>
       </c>
       <c r="B271" t="n">
         <v>43249</v>
@@ -30725,7 +30724,7 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J271" t="inlineStr"/>
@@ -30739,10 +30738,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>491738</v>
+        <v>491757</v>
       </c>
       <c r="R271" t="n">
-        <v>7016164</v>
+        <v>7016157</v>
       </c>
       <c r="S271" t="n">
         <v>25</v>
@@ -30801,13 +30800,13 @@
       <c r="AY271" t="inlineStr"/>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86410510</t>
+          <t>https://artportalen.se/Sighting/86410497</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>86410524</v>
+        <v>86410510</v>
       </c>
       <c r="B272" t="n">
         <v>43249</v>
@@ -30835,7 +30834,11 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I272" t="inlineStr"/>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
@@ -30847,10 +30850,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>491712</v>
+        <v>491738</v>
       </c>
       <c r="R272" t="n">
-        <v>7016175</v>
+        <v>7016164</v>
       </c>
       <c r="S272" t="n">
         <v>25</v>
@@ -30909,13 +30912,13 @@
       <c r="AY272" t="inlineStr"/>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86410524</t>
+          <t>https://artportalen.se/Sighting/86410510</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>86410541</v>
+        <v>86410524</v>
       </c>
       <c r="B273" t="n">
         <v>43249</v>
@@ -30943,11 +30946,7 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I273" t="inlineStr"/>
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
@@ -30959,10 +30958,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>491528</v>
+        <v>491712</v>
       </c>
       <c r="R273" t="n">
-        <v>7016224</v>
+        <v>7016175</v>
       </c>
       <c r="S273" t="n">
         <v>25</v>
@@ -31021,13 +31020,13 @@
       <c r="AY273" t="inlineStr"/>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86410541</t>
+          <t>https://artportalen.se/Sighting/86410524</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>86410556</v>
+        <v>86410541</v>
       </c>
       <c r="B274" t="n">
         <v>43249</v>
@@ -31071,10 +31070,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>490938</v>
+        <v>491528</v>
       </c>
       <c r="R274" t="n">
-        <v>7016381</v>
+        <v>7016224</v>
       </c>
       <c r="S274" t="n">
         <v>25</v>
@@ -31133,13 +31132,13 @@
       <c r="AY274" t="inlineStr"/>
       <c r="AZ274" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86410556</t>
+          <t>https://artportalen.se/Sighting/86410541</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>86410573</v>
+        <v>86410556</v>
       </c>
       <c r="B275" t="n">
         <v>43249</v>
@@ -31167,7 +31166,11 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I275" t="inlineStr"/>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
@@ -31179,10 +31182,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>490759</v>
+        <v>490938</v>
       </c>
       <c r="R275" t="n">
-        <v>7016431</v>
+        <v>7016381</v>
       </c>
       <c r="S275" t="n">
         <v>25</v>
@@ -31241,13 +31244,13 @@
       <c r="AY275" t="inlineStr"/>
       <c r="AZ275" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86410573</t>
+          <t>https://artportalen.se/Sighting/86410556</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>86410592</v>
+        <v>86410573</v>
       </c>
       <c r="B276" t="n">
         <v>43249</v>
@@ -31287,10 +31290,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>490593</v>
+        <v>490759</v>
       </c>
       <c r="R276" t="n">
-        <v>7016474</v>
+        <v>7016431</v>
       </c>
       <c r="S276" t="n">
         <v>25</v>
@@ -31349,64 +31352,59 @@
       <c r="AY276" t="inlineStr"/>
       <c r="AZ276" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86410592</t>
+          <t>https://artportalen.se/Sighting/86410573</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>121560121</v>
+        <v>86410592</v>
       </c>
       <c r="B277" t="n">
-        <v>101326</v>
+        <v>43249</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>222498</v>
+        <v>101248</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Violett guldvinge</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycaena helle</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
-      <c r="K277" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N277" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="inlineStr"/>
+      <c r="N277" t="inlineStr"/>
       <c r="P277" t="inlineStr">
         <is>
-          <t>Bäckmyren, Bäckmyren, Jmt</t>
+          <t>Bye, Jmt</t>
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>492551</v>
+        <v>490593</v>
       </c>
       <c r="R277" t="n">
-        <v>7015980</v>
+        <v>7016474</v>
       </c>
       <c r="S277" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T277" t="inlineStr">
         <is>
@@ -31430,12 +31428,12 @@
       </c>
       <c r="Y277" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2020-06-21</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2020-06-21</t>
         </is>
       </c>
       <c r="AD277" t="b">
@@ -31444,78 +31442,79 @@
       <c r="AE277" t="b">
         <v>0</v>
       </c>
+      <c r="AF277" t="inlineStr"/>
       <c r="AG277" t="b">
         <v>0</v>
-      </c>
-      <c r="AH277" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT277" t="inlineStr"/>
       <c r="AW277" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
       <c r="AZ277" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121560121</t>
+          <t>https://artportalen.se/Sighting/86410592</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>119817264</v>
+        <v>121560121</v>
       </c>
       <c r="B278" t="n">
-        <v>57953</v>
+        <v>101326</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
-      <c r="M278" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>Storfetten, Storfetten, Jmt</t>
+          <t>Bäckmyren, Bäckmyren, Jmt</t>
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>501579</v>
+        <v>492551</v>
       </c>
       <c r="R278" t="n">
-        <v>7014000</v>
+        <v>7015980</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -31542,17 +31541,12 @@
       </c>
       <c r="Y278" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
-        </is>
-      </c>
-      <c r="AC278" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AD278" t="b">
@@ -31563,31 +31557,36 @@
       </c>
       <c r="AG278" t="b">
         <v>0</v>
+      </c>
+      <c r="AH278" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT278" t="inlineStr"/>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119817264</t>
+          <t>https://artportalen.se/Sighting/121560121</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>133884020</v>
+        <v>119817264</v>
       </c>
       <c r="B279" t="n">
-        <v>58231</v>
+        <v>57953</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -31595,37 +31594,42 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>102980</v>
+        <v>100109</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>Fjälån, Jmt</t>
+          <t>Storfetten, Storfetten, Jmt</t>
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>500548</v>
+        <v>501579</v>
       </c>
       <c r="R279" t="n">
-        <v>7014163</v>
+        <v>7014000</v>
       </c>
       <c r="S279" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T279" t="inlineStr">
         <is>
@@ -31649,12 +31653,17 @@
       </c>
       <c r="Y279" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AC279" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD279" t="b">
@@ -31669,57 +31678,52 @@
       <c r="AT279" t="inlineStr"/>
       <c r="AW279" t="inlineStr">
         <is>
-          <t>Pattranit Kwanruen</t>
+          <t>Joel Schill</t>
         </is>
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>Pattranit Kwanruen</t>
+          <t>Joel Schill</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
       <c r="AZ279" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133884020</t>
+          <t>https://artportalen.se/Sighting/119817264</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>133884000</v>
+        <v>133884020</v>
       </c>
       <c r="B280" t="n">
-        <v>58234</v>
+        <v>58231</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>102981</v>
+        <v>102980</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
-      <c r="M280" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P280" t="inlineStr">
         <is>
           <t>Fjälån, Jmt</t>
@@ -31787,16 +31791,16 @@
       <c r="AY280" t="inlineStr"/>
       <c r="AZ280" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133884000</t>
+          <t>https://artportalen.se/Sighting/133884020</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>15772027</v>
+        <v>133884000</v>
       </c>
       <c r="B281" t="n">
-        <v>10000</v>
+        <v>58234</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -31804,41 +31808,42 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>100196</v>
+        <v>102981</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Hussvala</t>
+        </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Agathidium pallidum</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Gyllenhal, 1827)</t>
-        </is>
-      </c>
-      <c r="I281" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N281" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P281" t="inlineStr">
         <is>
-          <t>MidskogF14, Jmt</t>
+          <t>Fjälån, Jmt</t>
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>509456</v>
+        <v>500548</v>
       </c>
       <c r="R281" t="n">
-        <v>7012087</v>
+        <v>7014163</v>
       </c>
       <c r="S281" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
@@ -31862,17 +31867,12 @@
       </c>
       <c r="Y281" t="inlineStr">
         <is>
-          <t>2013-05-18</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
         <is>
-          <t>2013-06-21</t>
-        </is>
-      </c>
-      <c r="AC281" t="inlineStr">
-        <is>
-          <t>Lövbrännan med hög lövandel, mkt björk och en del asp, hyggligt med björkved</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD281" t="b">
@@ -31883,62 +31883,48 @@
       </c>
       <c r="AG281" t="b">
         <v>0</v>
-      </c>
-      <c r="AI281" t="inlineStr">
-        <is>
-          <t>Lövbränna, björkhögstubbe och låga, båda med fnösketickor.</t>
-        </is>
       </c>
       <c r="AT281" t="inlineStr"/>
       <c r="AW281" t="inlineStr">
         <is>
-          <t>Lars-Olof Grund</t>
+          <t>Pattranit Kwanruen</t>
         </is>
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>Lars-Olof Grund</t>
-        </is>
-      </c>
-      <c r="AY281" t="inlineStr">
-        <is>
-          <t>ÅGP-inventering björk och asp Norrland</t>
-        </is>
-      </c>
+          <t>Pattranit Kwanruen</t>
+        </is>
+      </c>
+      <c r="AY281" t="inlineStr"/>
       <c r="AZ281" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/15772027</t>
+          <t>https://artportalen.se/Sighting/133884000</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>15772038</v>
+        <v>15772027</v>
       </c>
       <c r="B282" t="n">
-        <v>8728</v>
+        <v>10000</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>100798</v>
-      </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>Smal trollknäppare</t>
-        </is>
+        <v>100196</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Danosoma conspersum</t>
+          <t>Agathidium pallidum</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Gyllenhal, 1808)</t>
+          <t>(Gyllenhal, 1827)</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -31987,12 +31973,12 @@
       </c>
       <c r="Y282" t="inlineStr">
         <is>
+          <t>2013-05-18</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
           <t>2013-06-21</t>
-        </is>
-      </c>
-      <c r="AA282" t="inlineStr">
-        <is>
-          <t>2013-07-18</t>
         </is>
       </c>
       <c r="AC282" t="inlineStr">
@@ -32032,38 +32018,38 @@
       </c>
       <c r="AZ282" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/15772038</t>
+          <t>https://artportalen.se/Sighting/15772027</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>15771999</v>
+        <v>15772038</v>
       </c>
       <c r="B283" t="n">
-        <v>4819</v>
+        <v>8728</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>100857</v>
+        <v>100798</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Robust tickgnagare</t>
+          <t>Smal trollknäppare</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Dorcatoma robusta</t>
+          <t>Danosoma conspersum</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Strand, 1938</t>
+          <t>(Gyllenhal, 1808)</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -32071,9 +32057,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>fönsterfälla</t>
+        </is>
+      </c>
       <c r="P283" t="inlineStr">
         <is>
-          <t>MidskogF13, Jmt</t>
+          <t>MidskogF14, Jmt</t>
         </is>
       </c>
       <c r="Q283" t="n">
@@ -32131,7 +32122,7 @@
       </c>
       <c r="AI283" t="inlineStr">
         <is>
-          <t>Lövbränna, asphögstubbe +låga</t>
+          <t>Lövbränna, björkhögstubbe och låga, båda med fnösketickor.</t>
         </is>
       </c>
       <c r="AT283" t="inlineStr"/>
@@ -32152,38 +32143,38 @@
       </c>
       <c r="AZ283" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/15771999</t>
+          <t>https://artportalen.se/Sighting/15772038</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>15772034</v>
+        <v>15771999</v>
       </c>
       <c r="B284" t="n">
-        <v>12370</v>
+        <v>4819</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>101465</v>
+        <v>100857</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Gulbandad brunbagge</t>
+          <t>Robust tickgnagare</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Orchesia fasciata</t>
+          <t>Dorcatoma robusta</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Illiger, 1798)</t>
+          <t>Strand, 1938</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -32191,14 +32182,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="N284" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
-        </is>
-      </c>
       <c r="P284" t="inlineStr">
         <is>
-          <t>MidskogF14, Jmt</t>
+          <t>MidskogF13, Jmt</t>
         </is>
       </c>
       <c r="Q284" t="n">
@@ -32232,12 +32218,12 @@
       </c>
       <c r="Y284" t="inlineStr">
         <is>
-          <t>2013-05-18</t>
+          <t>2013-06-21</t>
         </is>
       </c>
       <c r="AA284" t="inlineStr">
         <is>
-          <t>2013-06-21</t>
+          <t>2013-07-18</t>
         </is>
       </c>
       <c r="AC284" t="inlineStr">
@@ -32256,7 +32242,7 @@
       </c>
       <c r="AI284" t="inlineStr">
         <is>
-          <t>Lövbränna, björkhögstubbe och låga, båda med fnösketickor.</t>
+          <t>Lövbränna, asphögstubbe +låga</t>
         </is>
       </c>
       <c r="AT284" t="inlineStr"/>
@@ -32277,38 +32263,38 @@
       </c>
       <c r="AZ284" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/15772034</t>
+          <t>https://artportalen.se/Sighting/15771999</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>15771980</v>
+        <v>15772034</v>
       </c>
       <c r="B285" t="n">
-        <v>4872</v>
+        <v>12370</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>101675</v>
+        <v>101465</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Gulbandad brunbagge</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Orchesia fasciata</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Illiger, 1798)</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -32316,9 +32302,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>fönsterfälla</t>
+        </is>
+      </c>
       <c r="P285" t="inlineStr">
         <is>
-          <t>MidskogF13, Jmt</t>
+          <t>MidskogF14, Jmt</t>
         </is>
       </c>
       <c r="Q285" t="n">
@@ -32352,14 +32343,14 @@
       </c>
       <c r="Y285" t="inlineStr">
         <is>
+          <t>2013-05-18</t>
+        </is>
+      </c>
+      <c r="AA285" t="inlineStr">
+        <is>
           <t>2013-06-21</t>
         </is>
       </c>
-      <c r="AA285" t="inlineStr">
-        <is>
-          <t>2013-07-18</t>
-        </is>
-      </c>
       <c r="AC285" t="inlineStr">
         <is>
           <t>Lövbrännan med hög lövandel, mkt björk och en del asp, hyggligt med björkved</t>
@@ -32376,7 +32367,7 @@
       </c>
       <c r="AI285" t="inlineStr">
         <is>
-          <t>Lövbränna, asphögstubbe +låga</t>
+          <t>Lövbränna, björkhögstubbe och låga, båda med fnösketickor.</t>
         </is>
       </c>
       <c r="AT285" t="inlineStr"/>
@@ -32397,16 +32388,16 @@
       </c>
       <c r="AZ285" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/15771980</t>
+          <t>https://artportalen.se/Sighting/15772034</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>15772025</v>
+        <v>15771980</v>
       </c>
       <c r="B286" t="n">
-        <v>4813</v>
+        <v>4872</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32414,16 +32405,21 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>105333</v>
+        <v>101675</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Aspvedgnagare</t>
+        </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Dorcatoma dresdensis</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Herbst, 1792</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -32431,14 +32427,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="N286" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
-        </is>
-      </c>
       <c r="P286" t="inlineStr">
         <is>
-          <t>MidskogF14, Jmt</t>
+          <t>MidskogF13, Jmt</t>
         </is>
       </c>
       <c r="Q286" t="n">
@@ -32472,12 +32463,12 @@
       </c>
       <c r="Y286" t="inlineStr">
         <is>
-          <t>2013-05-18</t>
+          <t>2013-06-21</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
         <is>
-          <t>2013-06-21</t>
+          <t>2013-07-18</t>
         </is>
       </c>
       <c r="AC286" t="inlineStr">
@@ -32496,7 +32487,7 @@
       </c>
       <c r="AI286" t="inlineStr">
         <is>
-          <t>Lövbränna, björkhögstubbe och låga, båda med fnösketickor.</t>
+          <t>Lövbränna, asphögstubbe +låga</t>
         </is>
       </c>
       <c r="AT286" t="inlineStr"/>
@@ -32517,16 +32508,16 @@
       </c>
       <c r="AZ286" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/15772025</t>
+          <t>https://artportalen.se/Sighting/15771980</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>15772051</v>
+        <v>15772025</v>
       </c>
       <c r="B287" t="n">
-        <v>6274</v>
+        <v>4813</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -32534,21 +32525,16 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>105336</v>
-      </c>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>Vanlig flatbagge</t>
-        </is>
+        <v>105333</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Dorcatoma dresdensis</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Herbst, 1792</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -32597,12 +32583,12 @@
       </c>
       <c r="Y287" t="inlineStr">
         <is>
+          <t>2013-05-18</t>
+        </is>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
           <t>2013-06-21</t>
-        </is>
-      </c>
-      <c r="AA287" t="inlineStr">
-        <is>
-          <t>2013-07-18</t>
         </is>
       </c>
       <c r="AC287" t="inlineStr">
@@ -32641,6 +32627,131 @@
         </is>
       </c>
       <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15772025</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>15772051</v>
+      </c>
+      <c r="B288" t="n">
+        <v>6274</v>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>105336</v>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Vanlig flatbagge</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Peltis ferruginea</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>fönsterfälla</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>MidskogF14, Jmt</t>
+        </is>
+      </c>
+      <c r="Q288" t="n">
+        <v>509456</v>
+      </c>
+      <c r="R288" t="n">
+        <v>7012087</v>
+      </c>
+      <c r="S288" t="n">
+        <v>25</v>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W288" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y288" t="inlineStr">
+        <is>
+          <t>2013-06-21</t>
+        </is>
+      </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>2013-07-18</t>
+        </is>
+      </c>
+      <c r="AC288" t="inlineStr">
+        <is>
+          <t>Lövbrännan med hög lövandel, mkt björk och en del asp, hyggligt med björkved</t>
+        </is>
+      </c>
+      <c r="AD288" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE288" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG288" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI288" t="inlineStr">
+        <is>
+          <t>Lövbränna, björkhögstubbe och låga, båda med fnösketickor.</t>
+        </is>
+      </c>
+      <c r="AT288" t="inlineStr"/>
+      <c r="AW288" t="inlineStr">
+        <is>
+          <t>Lars-Olof Grund</t>
+        </is>
+      </c>
+      <c r="AX288" t="inlineStr">
+        <is>
+          <t>Lars-Olof Grund</t>
+        </is>
+      </c>
+      <c r="AY288" t="inlineStr">
+        <is>
+          <t>ÅGP-inventering björk och asp Norrland</t>
+        </is>
+      </c>
+      <c r="AZ288" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/15772051</t>
         </is>
@@ -32934,6 +33045,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -1157,7 +1157,7 @@
         <v>135817118</v>
       </c>
       <c r="B6" t="n">
-        <v>106607</v>
+        <v>106613</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136150004</v>
       </c>
       <c r="B23" t="n">
-        <v>89433</v>
+        <v>89439</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>136149902</v>
       </c>
       <c r="B24" t="n">
-        <v>92640</v>
+        <v>92646</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>136148101</v>
       </c>
       <c r="B27" t="n">
-        <v>89297</v>
+        <v>89303</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>136148724</v>
       </c>
       <c r="B31" t="n">
-        <v>58087</v>
+        <v>58091</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>136271230</v>
       </c>
       <c r="B109" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>136168429</v>
       </c>
       <c r="B110" t="n">
-        <v>79724</v>
+        <v>79728</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>136177837</v>
       </c>
       <c r="B207" t="n">
-        <v>106607</v>
+        <v>106613</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -1157,7 +1157,7 @@
         <v>135817118</v>
       </c>
       <c r="B6" t="n">
-        <v>106613</v>
+        <v>106614</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136150004</v>
       </c>
       <c r="B23" t="n">
-        <v>89439</v>
+        <v>89440</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>136149902</v>
       </c>
       <c r="B24" t="n">
-        <v>92646</v>
+        <v>92647</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>136148101</v>
       </c>
       <c r="B27" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>136148724</v>
       </c>
       <c r="B31" t="n">
-        <v>58091</v>
+        <v>58092</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>136271230</v>
       </c>
       <c r="B109" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>136168429</v>
       </c>
       <c r="B110" t="n">
-        <v>79728</v>
+        <v>79729</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>136177837</v>
       </c>
       <c r="B207" t="n">
-        <v>106613</v>
+        <v>106614</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -1157,7 +1157,7 @@
         <v>135817118</v>
       </c>
       <c r="B6" t="n">
-        <v>106614</v>
+        <v>106625</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136150004</v>
       </c>
       <c r="B23" t="n">
-        <v>89440</v>
+        <v>89446</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>136149902</v>
       </c>
       <c r="B24" t="n">
-        <v>92647</v>
+        <v>92653</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>136148101</v>
       </c>
       <c r="B27" t="n">
-        <v>89304</v>
+        <v>89310</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>136271230</v>
       </c>
       <c r="B109" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>136168429</v>
       </c>
       <c r="B110" t="n">
-        <v>79729</v>
+        <v>79733</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>136177837</v>
       </c>
       <c r="B207" t="n">
-        <v>106614</v>
+        <v>106625</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -1157,7 +1157,7 @@
         <v>135817118</v>
       </c>
       <c r="B6" t="n">
-        <v>106625</v>
+        <v>106638</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136150004</v>
       </c>
       <c r="B23" t="n">
-        <v>89446</v>
+        <v>89453</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>136149902</v>
       </c>
       <c r="B24" t="n">
-        <v>92653</v>
+        <v>92660</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>136148101</v>
       </c>
       <c r="B27" t="n">
-        <v>89310</v>
+        <v>89317</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>136148724</v>
       </c>
       <c r="B31" t="n">
-        <v>58092</v>
+        <v>58097</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>136271230</v>
       </c>
       <c r="B109" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>136168429</v>
       </c>
       <c r="B110" t="n">
-        <v>79733</v>
+        <v>79739</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>136177837</v>
       </c>
       <c r="B207" t="n">
-        <v>106625</v>
+        <v>106638</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -1157,7 +1157,7 @@
         <v>135817118</v>
       </c>
       <c r="B6" t="n">
-        <v>106638</v>
+        <v>106639</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136150004</v>
       </c>
       <c r="B23" t="n">
-        <v>89453</v>
+        <v>89454</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>136149902</v>
       </c>
       <c r="B24" t="n">
-        <v>92660</v>
+        <v>92661</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>136148101</v>
       </c>
       <c r="B27" t="n">
-        <v>89317</v>
+        <v>89318</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>136271230</v>
       </c>
       <c r="B109" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>136177837</v>
       </c>
       <c r="B207" t="n">
-        <v>106638</v>
+        <v>106639</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -1157,7 +1157,7 @@
         <v>135817118</v>
       </c>
       <c r="B6" t="n">
-        <v>106639</v>
+        <v>106652</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136150004</v>
       </c>
       <c r="B23" t="n">
-        <v>89454</v>
+        <v>89467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>136149902</v>
       </c>
       <c r="B24" t="n">
-        <v>92661</v>
+        <v>92674</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>136148101</v>
       </c>
       <c r="B27" t="n">
-        <v>89318</v>
+        <v>89331</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>136148724</v>
       </c>
       <c r="B31" t="n">
-        <v>58097</v>
+        <v>58110</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>136271230</v>
       </c>
       <c r="B109" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>136168429</v>
       </c>
       <c r="B110" t="n">
-        <v>79739</v>
+        <v>79752</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>136177837</v>
       </c>
       <c r="B207" t="n">
-        <v>106639</v>
+        <v>106652</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>

--- a/artfynd/S 448-2025 artfynd.xlsx
+++ b/artfynd/S 448-2025 artfynd.xlsx
@@ -3072,7 +3072,7 @@
         <v>136150004</v>
       </c>
       <c r="B23" t="n">
-        <v>89467</v>
+        <v>89468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>136149902</v>
       </c>
       <c r="B24" t="n">
-        <v>92674</v>
+        <v>92675</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>136148101</v>
       </c>
       <c r="B27" t="n">
-        <v>89331</v>
+        <v>89332</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>136271230</v>
       </c>
       <c r="B109" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>136168429</v>
       </c>
       <c r="B110" t="n">
-        <v>79752</v>
+        <v>79753</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>136177837</v>
       </c>
       <c r="B207" t="n">
-        <v>106652</v>
+        <v>106653</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
